--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="686" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1029" uniqueCount="81">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1029" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2325" uniqueCount="91">
   <si>
     <t>pull_province</t>
   </si>
@@ -256,6 +256,36 @@
   </si>
   <si>
     <t>conventional_nsu</t>
+  </si>
+  <si>
+    <t>HAMTIC</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>drop_reason</t>
+  </si>
+  <si>
+    <t>ambiguous quantity</t>
+  </si>
+  <si>
+    <t>standard quantity</t>
+  </si>
+  <si>
+    <t>3PQJGPX2</t>
+  </si>
+  <si>
+    <t>81YD2D4Y</t>
+  </si>
+  <si>
+    <t>K7QZ5BIX</t>
+  </si>
+  <si>
+    <t>UECM6ZZ7</t>
+  </si>
+  <si>
+    <t>7E61LTA6</t>
   </si>
 </sst>
 </file>
@@ -301,7 +331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -318,187 +348,202 @@
         <v>21</v>
       </c>
       <c r="E1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>36</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>66</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>67</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>71</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>72</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>73</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="1">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1">
         <v>2</v>
       </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="1">
-        <v>500</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
+      <c r="K2" s="1">
+        <v>220</v>
       </c>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="1">
-        <v>3</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="1"/>
+      <c r="J3" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="1">
-        <v>500</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
+      <c r="K3" s="1">
+        <v>0.2199999988079071</v>
       </c>
       <c r="L3" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="1">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="1">
-        <v>500</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
+      <c r="K4" s="1">
+        <v>0.25999999046325684</v>
       </c>
       <c r="L4" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>76</v>
+        <v>27</v>
+      </c>
+      <c r="N4" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="1">
-        <v>3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="1">
-        <v>500</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
+      <c r="K5" s="1">
+        <v>170</v>
       </c>
       <c r="L5" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="M5" t="s">
-        <v>76</v>
+        <v>27</v>
+      </c>
+      <c r="N5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -506,40 +551,41 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="1">
+        <v>84</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="1">
         <v>2</v>
       </c>
-      <c r="G6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="1">
-        <v>28.571428298950195</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="1">
-        <v>190</v>
-      </c>
-      <c r="K6" t="s">
-        <v>23</v>
+      <c r="K6" s="1">
+        <v>245</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M6" t="s">
-        <v>77</v>
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -547,122 +593,125 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="1">
-        <v>28.571428298950195</v>
-      </c>
-      <c r="I7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="1">
-        <v>250</v>
-      </c>
-      <c r="K7" t="s">
-        <v>23</v>
+      <c r="K7" s="1">
+        <v>0.20000000298023224</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M7" t="s">
-        <v>77</v>
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="1">
-        <v>28.571428298950195</v>
-      </c>
-      <c r="I8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" s="1">
-        <v>190</v>
-      </c>
-      <c r="K8" t="s">
-        <v>23</v>
+        <v>84</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0.5</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M8" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="N8" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="1">
-        <v>28.571428298950195</v>
-      </c>
-      <c r="I9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" s="1">
-        <v>175</v>
-      </c>
-      <c r="K9" t="s">
-        <v>23</v>
+      <c r="H9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0.5</v>
       </c>
       <c r="L9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="N9" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -670,79 +719,83 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="K10" t="s">
-        <v>24</v>
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="1">
+        <v>3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>88</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0.5</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="N10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="1">
-        <v>3</v>
-      </c>
-      <c r="G11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="1">
-        <v>125</v>
-      </c>
-      <c r="I11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="1">
-        <v>500</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="K11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="L11" t="s">
         <v>22</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>74</v>
       </c>
-      <c r="M11" t="s">
-        <v>77</v>
+      <c r="N11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -750,193 +803,208 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" s="1">
-        <v>350</v>
-      </c>
-      <c r="K12" t="s">
-        <v>26</v>
+        <v>84</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0.5</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M12" t="s">
-        <v>79</v>
+        <v>74</v>
+      </c>
+      <c r="N12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="1">
-        <v>350</v>
-      </c>
-      <c r="K13" t="s">
-        <v>26</v>
+      <c r="K13" s="1">
+        <v>500</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>79</v>
+        <v>74</v>
+      </c>
+      <c r="N13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="1"/>
-      <c r="I14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" t="s">
         <v>68</v>
       </c>
-      <c r="J14" s="1">
-        <v>350</v>
-      </c>
-      <c r="K14" t="s">
-        <v>26</v>
+      <c r="K14" s="1">
+        <v>500</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M14" t="s">
-        <v>79</v>
+        <v>74</v>
+      </c>
+      <c r="N14" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="1"/>
-      <c r="I15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" t="s">
         <v>68</v>
       </c>
-      <c r="J15" s="1">
-        <v>0.25999999046325684</v>
-      </c>
-      <c r="K15" t="s">
-        <v>27</v>
+      <c r="K15" s="1">
+        <v>500</v>
       </c>
       <c r="L15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="N15" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" t="s">
-        <v>51</v>
-      </c>
-      <c r="H16" s="1"/>
-      <c r="I16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" t="s">
         <v>68</v>
       </c>
-      <c r="J16" s="1">
-        <v>220</v>
-      </c>
-      <c r="K16" t="s">
-        <v>27</v>
+      <c r="K16" s="1">
+        <v>500</v>
       </c>
       <c r="L16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M16" t="s">
+        <v>74</v>
+      </c>
+      <c r="N16" t="s">
         <v>76</v>
       </c>
     </row>
@@ -945,38 +1013,43 @@
         <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H17" s="1"/>
-      <c r="I17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="1">
+        <v>28.571428298950195</v>
+      </c>
+      <c r="J17" t="s">
         <v>68</v>
       </c>
-      <c r="J17" s="1">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="K17" t="s">
-        <v>27</v>
+      <c r="K17" s="1">
+        <v>175</v>
       </c>
       <c r="L17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>79</v>
+        <v>23</v>
+      </c>
+      <c r="N17" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -984,38 +1057,43 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2</v>
-      </c>
-      <c r="G18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H18" s="1"/>
-      <c r="I18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="1">
+        <v>28.571428298950195</v>
+      </c>
+      <c r="J18" t="s">
         <v>68</v>
       </c>
-      <c r="J18" s="1">
-        <v>170</v>
-      </c>
-      <c r="K18" t="s">
-        <v>27</v>
+      <c r="K18" s="1">
+        <v>190</v>
       </c>
       <c r="L18" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>79</v>
+        <v>23</v>
+      </c>
+      <c r="N18" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19">
@@ -1023,38 +1101,43 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" t="s">
+        <v>85</v>
+      </c>
+      <c r="F19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" t="s">
+        <v>41</v>
+      </c>
+      <c r="I19" s="1">
+        <v>28.571428298950195</v>
+      </c>
+      <c r="J19" t="s">
         <v>68</v>
       </c>
-      <c r="J19" s="1">
-        <v>0.2199999988079071</v>
-      </c>
-      <c r="K19" t="s">
-        <v>27</v>
+      <c r="K19" s="1">
+        <v>190</v>
       </c>
       <c r="L19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M19" t="s">
-        <v>76</v>
+        <v>23</v>
+      </c>
+      <c r="N19" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="20">
@@ -1062,232 +1145,254 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2</v>
-      </c>
-      <c r="G20" t="s">
-        <v>51</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="1">
+        <v>28.571428298950195</v>
+      </c>
+      <c r="J20" t="s">
         <v>68</v>
       </c>
-      <c r="J20" s="1">
-        <v>245</v>
-      </c>
-      <c r="K20" t="s">
-        <v>27</v>
+      <c r="K20" s="1">
+        <v>250</v>
       </c>
       <c r="L20" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>78</v>
+        <v>23</v>
+      </c>
+      <c r="N20" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="1">
-        <v>3</v>
-      </c>
-      <c r="G21" t="s">
-        <v>52</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" t="s">
         <v>69</v>
       </c>
-      <c r="J21" s="1">
-        <v>21.004999160766602</v>
-      </c>
-      <c r="K21" t="s">
-        <v>28</v>
+      <c r="K21" s="1">
+        <v>1.5</v>
       </c>
       <c r="L21" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M21" t="s">
-        <v>76</v>
+        <v>24</v>
+      </c>
+      <c r="N21" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" s="1">
-        <v>3</v>
-      </c>
-      <c r="G22" t="s">
-        <v>53</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3</v>
+      </c>
+      <c r="H22" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="1">
+        <v>125</v>
+      </c>
+      <c r="J22" t="s">
         <v>70</v>
       </c>
-      <c r="J22" s="1">
-        <v>0.0060000000521540642</v>
-      </c>
-      <c r="K22" t="s">
-        <v>28</v>
+      <c r="K22" s="1">
+        <v>500</v>
       </c>
       <c r="L22" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M22" t="s">
-        <v>76</v>
+        <v>74</v>
+      </c>
+      <c r="N22" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" t="s">
-        <v>70</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0.0060000000521540642</v>
-      </c>
-      <c r="K23" t="s">
-        <v>28</v>
+        <v>85</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" s="1"/>
+      <c r="J23" t="s">
+        <v>68</v>
+      </c>
+      <c r="K23" s="1">
+        <v>350</v>
       </c>
       <c r="L23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="1">
-        <v>3</v>
-      </c>
-      <c r="G24" t="s">
-        <v>55</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" t="s">
-        <v>70</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0.0065999999642372131</v>
-      </c>
-      <c r="K24" t="s">
-        <v>28</v>
+        <v>85</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="1"/>
+      <c r="J24" t="s">
+        <v>68</v>
+      </c>
+      <c r="K24" s="1">
+        <v>350</v>
       </c>
       <c r="L24" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>76</v>
+        <v>26</v>
+      </c>
+      <c r="N24" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" t="s">
-        <v>56</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" t="s">
-        <v>70</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0.0060000000521540642</v>
-      </c>
-      <c r="K25" t="s">
-        <v>28</v>
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1</v>
+      </c>
+      <c r="H25" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="1"/>
+      <c r="J25" t="s">
+        <v>68</v>
+      </c>
+      <c r="K25" s="1">
+        <v>350</v>
       </c>
       <c r="L25" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M25" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1305,29 +1410,32 @@
         <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" s="1"/>
-      <c r="I26" t="s">
-        <v>69</v>
-      </c>
-      <c r="J26" s="1">
-        <v>21.479999542236328</v>
-      </c>
-      <c r="K26" t="s">
-        <v>28</v>
+        <v>85</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="1"/>
+      <c r="J26" t="s">
+        <v>70</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L26" t="s">
         <v>28</v>
       </c>
       <c r="M26" t="s">
-        <v>76</v>
+        <v>28</v>
+      </c>
+      <c r="N26" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="27">
@@ -1344,28 +1452,31 @@
         <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" t="s">
+        <v>85</v>
+      </c>
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" t="s">
         <v>58</v>
       </c>
-      <c r="H27" s="1"/>
-      <c r="I27" t="s">
+      <c r="I27" s="1"/>
+      <c r="J27" t="s">
         <v>70</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>6</v>
       </c>
-      <c r="K27" t="s">
-        <v>28</v>
-      </c>
       <c r="L27" t="s">
         <v>28</v>
       </c>
       <c r="M27" t="s">
+        <v>28</v>
+      </c>
+      <c r="N27" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1383,28 +1494,31 @@
         <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2</v>
-      </c>
-      <c r="G28" t="s">
-        <v>59</v>
-      </c>
-      <c r="H28" s="1"/>
-      <c r="I28" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="1">
+        <v>3</v>
+      </c>
+      <c r="H28" t="s">
+        <v>52</v>
+      </c>
+      <c r="I28" s="1"/>
+      <c r="J28" t="s">
         <v>69</v>
       </c>
-      <c r="J28" s="1">
-        <v>21.670000076293945</v>
-      </c>
-      <c r="K28" t="s">
-        <v>28</v>
+      <c r="K28" s="1">
+        <v>21.004999160766602</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
       </c>
       <c r="M28" t="s">
+        <v>28</v>
+      </c>
+      <c r="N28" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1419,32 +1533,35 @@
         <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="1">
-        <v>3</v>
-      </c>
-      <c r="G29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="1"/>
-      <c r="I29" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="1">
+        <v>3</v>
+      </c>
+      <c r="H29" t="s">
+        <v>53</v>
+      </c>
+      <c r="I29" s="1"/>
+      <c r="J29" t="s">
         <v>70</v>
       </c>
-      <c r="J29" s="1">
-        <v>0.0099999997764825821</v>
-      </c>
-      <c r="K29" t="s">
-        <v>29</v>
+      <c r="K29" s="1">
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M29" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="N29" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="30">
@@ -1458,32 +1575,35 @@
         <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30" t="s">
+        <v>85</v>
+      </c>
+      <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="1">
+        <v>3</v>
+      </c>
+      <c r="H30" t="s">
+        <v>55</v>
+      </c>
+      <c r="I30" s="1"/>
+      <c r="J30" t="s">
         <v>70</v>
       </c>
-      <c r="J30" s="1">
-        <v>0.0099999997764825821</v>
-      </c>
-      <c r="K30" t="s">
-        <v>29</v>
+      <c r="K30" s="1">
+        <v>0.0065999999642372131</v>
       </c>
       <c r="L30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M30" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="N30" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="31">
@@ -1497,32 +1617,35 @@
         <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="I31" t="s">
-        <v>70</v>
-      </c>
-      <c r="J31" s="1">
-        <v>0.0099999997764825821</v>
-      </c>
-      <c r="K31" t="s">
-        <v>29</v>
+        <v>85</v>
+      </c>
+      <c r="F31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" t="s">
+        <v>57</v>
+      </c>
+      <c r="I31" s="1"/>
+      <c r="J31" t="s">
+        <v>69</v>
+      </c>
+      <c r="K31" s="1">
+        <v>21.479999542236328</v>
       </c>
       <c r="L31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M31" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="N31" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="32">
@@ -1536,32 +1659,35 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" t="s">
-        <v>63</v>
-      </c>
-      <c r="H32" s="1"/>
-      <c r="I32" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
+      <c r="H32" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" s="1"/>
+      <c r="J32" t="s">
         <v>70</v>
       </c>
-      <c r="J32" s="1">
-        <v>0.0099999997764825821</v>
-      </c>
-      <c r="K32" t="s">
-        <v>29</v>
+      <c r="K32" s="1">
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M32" t="s">
-        <v>78</v>
+        <v>28</v>
+      </c>
+      <c r="N32" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="33">
@@ -1569,38 +1695,41 @@
         <v>4</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="I33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="1"/>
+      <c r="J33" t="s">
         <v>69</v>
       </c>
-      <c r="J33" s="1">
-        <v>25</v>
-      </c>
-      <c r="K33" t="s">
-        <v>30</v>
+      <c r="K33" s="1">
+        <v>21.670000076293945</v>
       </c>
       <c r="L33" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M33" t="s">
-        <v>80</v>
+        <v>28</v>
+      </c>
+      <c r="N33" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="34">
@@ -1608,37 +1737,250 @@
         <v>4</v>
       </c>
       <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>29</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="H34" t="s">
+        <v>62</v>
+      </c>
+      <c r="I34" s="1"/>
+      <c r="J34" t="s">
+        <v>70</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L34" t="s">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s">
+        <v>29</v>
+      </c>
+      <c r="N34" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>85</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="H35" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" t="s">
+        <v>70</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L35" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35" t="s">
+        <v>29</v>
+      </c>
+      <c r="N35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>29</v>
+      </c>
+      <c r="E36" t="s">
+        <v>85</v>
+      </c>
+      <c r="F36" t="s">
+        <v>32</v>
+      </c>
+      <c r="G36" s="1">
+        <v>3</v>
+      </c>
+      <c r="H36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I36" s="1"/>
+      <c r="J36" t="s">
+        <v>70</v>
+      </c>
+      <c r="K36" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L36" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" t="s">
+        <v>29</v>
+      </c>
+      <c r="N36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" t="s">
+        <v>32</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>63</v>
+      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" t="s">
+        <v>70</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L37" t="s">
+        <v>29</v>
+      </c>
+      <c r="M37" t="s">
+        <v>29</v>
+      </c>
+      <c r="N37" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" t="s">
         <v>12</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C38" t="s">
         <v>20</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D38" t="s">
         <v>30</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F38" t="s">
         <v>34</v>
       </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" t="s">
         <v>65</v>
       </c>
-      <c r="H34" s="1"/>
-      <c r="I34" t="s">
+      <c r="I38" s="1"/>
+      <c r="J38" t="s">
         <v>69</v>
       </c>
-      <c r="J34" s="1">
+      <c r="K38" s="1">
         <v>25</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L38" t="s">
         <v>30</v>
       </c>
-      <c r="L34" t="s">
+      <c r="M38" t="s">
         <v>30</v>
       </c>
-      <c r="M34" t="s">
+      <c r="N38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" t="s">
+        <v>85</v>
+      </c>
+      <c r="F39" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="1">
+        <v>1</v>
+      </c>
+      <c r="H39" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" s="1"/>
+      <c r="J39" t="s">
+        <v>69</v>
+      </c>
+      <c r="K39" s="1">
+        <v>25</v>
+      </c>
+      <c r="L39" t="s">
+        <v>30</v>
+      </c>
+      <c r="M39" t="s">
+        <v>30</v>
+      </c>
+      <c r="N39" t="s">
         <v>80</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2325" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3621" uniqueCount="91">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3621" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4917" uniqueCount="91">
   <si>
     <t>pull_province</t>
   </si>
@@ -408,7 +408,7 @@
         <v>68</v>
       </c>
       <c r="K2" s="1">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="L2" t="s">
         <v>27</v>
@@ -417,7 +417,7 @@
         <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -450,7 +450,7 @@
         <v>68</v>
       </c>
       <c r="K3" s="1">
-        <v>0.2199999988079071</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="L3" t="s">
         <v>27</v>
@@ -459,7 +459,7 @@
         <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -482,17 +482,17 @@
         <v>32</v>
       </c>
       <c r="G4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>68</v>
       </c>
       <c r="K4" s="1">
-        <v>0.25999999046325684</v>
+        <v>220</v>
       </c>
       <c r="L4" t="s">
         <v>27</v>
@@ -501,7 +501,7 @@
         <v>27</v>
       </c>
       <c r="N4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -524,17 +524,17 @@
         <v>32</v>
       </c>
       <c r="G5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" t="s">
         <v>68</v>
       </c>
       <c r="K5" s="1">
-        <v>170</v>
+        <v>0.2199999988079071</v>
       </c>
       <c r="L5" t="s">
         <v>27</v>
@@ -543,7 +543,7 @@
         <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -566,17 +566,17 @@
         <v>32</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" t="s">
         <v>68</v>
       </c>
       <c r="K6" s="1">
-        <v>245</v>
+        <v>0.20000000298023224</v>
       </c>
       <c r="L6" t="s">
         <v>27</v>
@@ -585,7 +585,7 @@
         <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -608,17 +608,17 @@
         <v>32</v>
       </c>
       <c r="G7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" t="s">
         <v>68</v>
       </c>
       <c r="K7" s="1">
-        <v>0.20000000298023224</v>
+        <v>170</v>
       </c>
       <c r="L7" t="s">
         <v>27</v>
@@ -692,10 +692,10 @@
         <v>32</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" t="s">
@@ -779,7 +779,7 @@
         <v>3</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" t="s">
@@ -818,10 +818,10 @@
         <v>32</v>
       </c>
       <c r="G12" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" t="s">
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" t="s">
@@ -902,10 +902,10 @@
         <v>32</v>
       </c>
       <c r="G14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" t="s">
@@ -986,10 +986,10 @@
         <v>32</v>
       </c>
       <c r="G16" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" t="s">
@@ -1028,10 +1028,10 @@
         <v>33</v>
       </c>
       <c r="G17" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I17" s="1">
         <v>28.571428298950195</v>
@@ -1040,7 +1040,7 @@
         <v>68</v>
       </c>
       <c r="K17" s="1">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="L17" t="s">
         <v>23</v>
@@ -1160,10 +1160,10 @@
         <v>33</v>
       </c>
       <c r="G20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I20" s="1">
         <v>28.571428298950195</v>
@@ -1172,7 +1172,7 @@
         <v>68</v>
       </c>
       <c r="K20" s="1">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="L20" t="s">
         <v>23</v>
@@ -1293,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" t="s">
@@ -1335,7 +1335,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I24" s="1"/>
       <c r="J24" t="s">
@@ -1416,10 +1416,10 @@
         <v>32</v>
       </c>
       <c r="G26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I26" s="1"/>
       <c r="J26" t="s">
@@ -1435,7 +1435,7 @@
         <v>28</v>
       </c>
       <c r="N26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -1461,14 +1461,14 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" t="s">
         <v>70</v>
       </c>
       <c r="K27" s="1">
-        <v>6</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L27" t="s">
         <v>28</v>
@@ -1477,7 +1477,7 @@
         <v>28</v>
       </c>
       <c r="N27" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
@@ -1542,17 +1542,17 @@
         <v>32</v>
       </c>
       <c r="G29" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K29" s="1">
-        <v>0.0060000000521540642</v>
+        <v>21.670000076293945</v>
       </c>
       <c r="L29" t="s">
         <v>28</v>
@@ -1626,17 +1626,17 @@
         <v>32</v>
       </c>
       <c r="G31" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K31" s="1">
-        <v>21.479999542236328</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L31" t="s">
         <v>28</v>
@@ -1645,7 +1645,7 @@
         <v>28</v>
       </c>
       <c r="N31" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32">
@@ -1668,17 +1668,17 @@
         <v>32</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K32" s="1">
-        <v>0.0060000000521540642</v>
+        <v>21.479999542236328</v>
       </c>
       <c r="L32" t="s">
         <v>28</v>
@@ -1687,7 +1687,7 @@
         <v>28</v>
       </c>
       <c r="N32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
@@ -1710,17 +1710,17 @@
         <v>32</v>
       </c>
       <c r="G33" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K33" s="1">
-        <v>21.670000076293945</v>
+        <v>6</v>
       </c>
       <c r="L33" t="s">
         <v>28</v>
@@ -1794,10 +1794,10 @@
         <v>32</v>
       </c>
       <c r="G35" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" t="s">
@@ -1836,10 +1836,10 @@
         <v>32</v>
       </c>
       <c r="G36" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" t="s">

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4917" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="7509" uniqueCount="91">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="7509" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="7985" uniqueCount="98">
   <si>
     <t>pull_province</t>
   </si>
@@ -286,6 +286,27 @@
   </si>
   <si>
     <t>7E61LTA6</t>
+  </si>
+  <si>
+    <t>DUEAS</t>
+  </si>
+  <si>
+    <t>cabbage</t>
+  </si>
+  <si>
+    <t>2 kapinutos nga cabbage/20pesos</t>
+  </si>
+  <si>
+    <t>KED6C3DL</t>
+  </si>
+  <si>
+    <t>PTGS9CZB</t>
+  </si>
+  <si>
+    <t>AG60CRCP</t>
+  </si>
+  <si>
+    <t>ANAOAQ31</t>
   </si>
 </sst>
 </file>
@@ -331,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -380,16 +401,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
         <v>84</v>
@@ -398,40 +419,40 @@
         <v>32</v>
       </c>
       <c r="G2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" t="s">
         <v>68</v>
       </c>
       <c r="K2" s="1">
-        <v>245</v>
+        <v>330</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="N2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>84</v>
@@ -443,37 +464,37 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" t="s">
         <v>68</v>
       </c>
       <c r="K3" s="1">
-        <v>0.25999999046325684</v>
+        <v>235</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>84</v>
@@ -485,37 +506,37 @@
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>68</v>
       </c>
       <c r="K4" s="1">
-        <v>220</v>
+        <v>325</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="N4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>84</v>
@@ -527,23 +548,23 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" t="s">
         <v>68</v>
       </c>
       <c r="K5" s="1">
-        <v>0.2199999988079071</v>
+        <v>285</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="M5" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="N5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -566,17 +587,17 @@
         <v>32</v>
       </c>
       <c r="G6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" t="s">
         <v>68</v>
       </c>
       <c r="K6" s="1">
-        <v>0.20000000298023224</v>
+        <v>220</v>
       </c>
       <c r="L6" t="s">
         <v>27</v>
@@ -585,7 +606,7 @@
         <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +639,7 @@
         <v>68</v>
       </c>
       <c r="K7" s="1">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="L7" t="s">
         <v>27</v>
@@ -627,21 +648,21 @@
         <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
         <v>84</v>
@@ -653,37 +674,37 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K8" s="1">
-        <v>0.5</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="L8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M8" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="N8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
         <v>84</v>
@@ -692,40 +713,40 @@
         <v>32</v>
       </c>
       <c r="G9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K9" s="1">
-        <v>0.5</v>
+        <v>170</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
         <v>84</v>
@@ -734,23 +755,23 @@
         <v>32</v>
       </c>
       <c r="G10" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K10" s="1">
-        <v>0.5</v>
+        <v>0.2199999988079071</v>
       </c>
       <c r="L10" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="N10" t="s">
         <v>76</v>
@@ -758,16 +779,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
         <v>84</v>
@@ -776,26 +797,26 @@
         <v>32</v>
       </c>
       <c r="G11" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K11" s="1">
-        <v>0.5</v>
+        <v>0.20000000298023224</v>
       </c>
       <c r="L11" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="N11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12">
@@ -818,10 +839,10 @@
         <v>32</v>
       </c>
       <c r="G12" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" t="s">
@@ -842,19 +863,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" t="s">
         <v>32</v>
@@ -863,14 +884,14 @@
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K13" s="1">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="L13" t="s">
         <v>22</v>
@@ -884,19 +905,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
         <v>32</v>
@@ -905,14 +926,14 @@
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K14" s="1">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="L14" t="s">
         <v>22</v>
@@ -926,35 +947,35 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
         <v>32</v>
       </c>
       <c r="G15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K15" s="1">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="L15" t="s">
         <v>22</v>
@@ -968,35 +989,35 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
         <v>32</v>
       </c>
       <c r="G16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K16" s="1">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="L16" t="s">
         <v>22</v>
@@ -1010,220 +1031,214 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="1">
         <v>2</v>
       </c>
-      <c r="B17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>85</v>
-      </c>
-      <c r="F17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="1">
-        <v>3</v>
-      </c>
       <c r="H17" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="1">
-        <v>28.571428298950195</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="I17" s="1"/>
       <c r="J17" t="s">
         <v>68</v>
       </c>
       <c r="K17" s="1">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="N17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
         <v>85</v>
       </c>
       <c r="F18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G18" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="1">
-        <v>28.571428298950195</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="I18" s="1"/>
       <c r="J18" t="s">
         <v>68</v>
       </c>
       <c r="K18" s="1">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M18" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="N18" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
         <v>85</v>
       </c>
       <c r="F19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" s="1">
-        <v>28.571428298950195</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="I19" s="1"/>
       <c r="J19" t="s">
         <v>68</v>
       </c>
       <c r="K19" s="1">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="N19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
         <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G20" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="1">
-        <v>28.571428298950195</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="I20" s="1"/>
       <c r="J20" t="s">
         <v>68</v>
       </c>
       <c r="K20" s="1">
-        <v>175</v>
+        <v>500</v>
       </c>
       <c r="L20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M20" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
         <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>45</v>
-      </c>
-      <c r="I21" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="I21" s="1">
+        <v>28.571428298950195</v>
+      </c>
       <c r="J21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K21" s="1">
-        <v>1.5</v>
+        <v>190</v>
       </c>
       <c r="L21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -1231,13 +1246,13 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
@@ -1246,25 +1261,25 @@
         <v>33</v>
       </c>
       <c r="G22" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I22" s="1">
-        <v>125</v>
+        <v>28.571428298950195</v>
       </c>
       <c r="J22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K22" s="1">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="N22" t="s">
         <v>77</v>
@@ -1272,86 +1287,90 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E23" t="s">
         <v>85</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
-      </c>
-      <c r="I23" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="I23" s="1">
+        <v>28.571428298950195</v>
+      </c>
       <c r="J23" t="s">
         <v>68</v>
       </c>
       <c r="K23" s="1">
-        <v>350</v>
+        <v>175</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
       <c r="H24" t="s">
-        <v>47</v>
-      </c>
-      <c r="I24" s="1"/>
+        <v>42</v>
+      </c>
+      <c r="I24" s="1">
+        <v>28.571428298950195</v>
+      </c>
       <c r="J24" t="s">
         <v>68</v>
       </c>
       <c r="K24" s="1">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -1362,10 +1381,10 @@
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
         <v>85</v>
@@ -1377,79 +1396,81 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K25" s="1">
-        <v>350</v>
+        <v>1.5</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
         <v>85</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" s="1">
         <v>3</v>
       </c>
       <c r="H26" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="I26" s="1">
+        <v>125</v>
+      </c>
       <c r="J26" t="s">
         <v>70</v>
       </c>
       <c r="K26" s="1">
-        <v>0.0060000000521540642</v>
+        <v>500</v>
       </c>
       <c r="L26" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M26" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="N26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
         <v>85</v>
@@ -1461,20 +1482,20 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K27" s="1">
-        <v>0.0060000000521540642</v>
+        <v>350</v>
       </c>
       <c r="L27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
         <v>79</v>
@@ -1482,16 +1503,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E28" t="s">
         <v>85</v>
@@ -1500,40 +1521,40 @@
         <v>32</v>
       </c>
       <c r="G28" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K28" s="1">
-        <v>21.004999160766602</v>
+        <v>350</v>
       </c>
       <c r="L28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
         <v>85</v>
@@ -1542,26 +1563,26 @@
         <v>32</v>
       </c>
       <c r="G29" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K29" s="1">
-        <v>21.670000076293945</v>
+        <v>350</v>
       </c>
       <c r="L29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M29" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
@@ -1584,17 +1605,17 @@
         <v>32</v>
       </c>
       <c r="G30" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" t="s">
         <v>70</v>
       </c>
       <c r="K30" s="1">
-        <v>0.0065999999642372131</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -1603,7 +1624,7 @@
         <v>28</v>
       </c>
       <c r="N30" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
@@ -1626,17 +1647,17 @@
         <v>32</v>
       </c>
       <c r="G31" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" t="s">
         <v>70</v>
       </c>
       <c r="K31" s="1">
-        <v>0.0060000000521540642</v>
+        <v>0.0065999999642372131</v>
       </c>
       <c r="L31" t="s">
         <v>28</v>
@@ -1645,7 +1666,7 @@
         <v>28</v>
       </c>
       <c r="N31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32">
@@ -1668,17 +1689,17 @@
         <v>32</v>
       </c>
       <c r="G32" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K32" s="1">
-        <v>21.479999542236328</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L32" t="s">
         <v>28</v>
@@ -1687,7 +1708,7 @@
         <v>28</v>
       </c>
       <c r="N32" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
@@ -1710,17 +1731,17 @@
         <v>32</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K33" s="1">
-        <v>6</v>
+        <v>21.004999160766602</v>
       </c>
       <c r="L33" t="s">
         <v>28</v>
@@ -1743,7 +1764,7 @@
         <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
         <v>85</v>
@@ -1755,23 +1776,23 @@
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" t="s">
         <v>70</v>
       </c>
       <c r="K34" s="1">
-        <v>0.0099999997764825821</v>
+        <v>6</v>
       </c>
       <c r="L34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35">
@@ -1785,7 +1806,7 @@
         <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E35" t="s">
         <v>85</v>
@@ -1797,23 +1818,23 @@
         <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" t="s">
         <v>70</v>
       </c>
       <c r="K35" s="1">
-        <v>0.0099999997764825821</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36">
@@ -1827,7 +1848,7 @@
         <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
         <v>85</v>
@@ -1836,26 +1857,26 @@
         <v>32</v>
       </c>
       <c r="G36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K36" s="1">
-        <v>0.0099999997764825821</v>
+        <v>21.670000076293945</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
@@ -1869,7 +1890,7 @@
         <v>19</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
         <v>85</v>
@@ -1878,26 +1899,26 @@
         <v>32</v>
       </c>
       <c r="G37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K37" s="1">
-        <v>0.0099999997764825821</v>
+        <v>21.479999542236328</v>
       </c>
       <c r="L37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N37" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38">
@@ -1905,41 +1926,41 @@
         <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
         <v>85</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K38" s="1">
-        <v>25</v>
+        <v>0.0099999997764825821</v>
       </c>
       <c r="L38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
@@ -1947,40 +1968,208 @@
         <v>4</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E39" t="s">
         <v>85</v>
       </c>
       <c r="F39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" t="s">
+        <v>70</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L39" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" t="s">
+        <v>29</v>
+      </c>
+      <c r="N39" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" t="s">
+        <v>32</v>
+      </c>
+      <c r="G40" s="1">
+        <v>3</v>
+      </c>
+      <c r="H40" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" t="s">
+        <v>70</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L40" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40" t="s">
+        <v>29</v>
+      </c>
+      <c r="N40" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>61</v>
+      </c>
+      <c r="I41" s="1"/>
+      <c r="J41" t="s">
+        <v>70</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L41" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" t="s">
+        <v>29</v>
+      </c>
+      <c r="N41" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>30</v>
+      </c>
+      <c r="E42" t="s">
+        <v>85</v>
+      </c>
+      <c r="F42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>64</v>
+      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" t="s">
         <v>69</v>
       </c>
-      <c r="K39" s="1">
+      <c r="K42" s="1">
         <v>25</v>
       </c>
-      <c r="L39" t="s">
+      <c r="L42" t="s">
         <v>30</v>
       </c>
-      <c r="M39" t="s">
+      <c r="M42" t="s">
         <v>30</v>
       </c>
-      <c r="N39" t="s">
+      <c r="N42" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>30</v>
+      </c>
+      <c r="E43" t="s">
+        <v>85</v>
+      </c>
+      <c r="F43" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="1"/>
+      <c r="J43" t="s">
+        <v>69</v>
+      </c>
+      <c r="K43" s="1">
+        <v>25</v>
+      </c>
+      <c r="L43" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43" t="s">
+        <v>30</v>
+      </c>
+      <c r="N43" t="s">
         <v>80</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,26 +13,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="7985" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="476" uniqueCount="98">
   <si>
     <t>pull_province</t>
   </si>
   <si>
+    <t>ILOILO</t>
+  </si>
+  <si>
+    <t>CAPIZ</t>
+  </si>
+  <si>
+    <t>ANTIQUE</t>
+  </si>
+  <si>
     <t>AKLAN</t>
   </si>
   <si>
-    <t>CAPIZ</t>
-  </si>
-  <si>
-    <t>ANTIQUE</t>
-  </si>
-  <si>
-    <t>ILOILO</t>
-  </si>
-  <si>
     <t>pull_municipal_city</t>
   </si>
   <si>
+    <t>DUEAS</t>
+  </si>
+  <si>
+    <t>PILAR</t>
+  </si>
+  <si>
+    <t>HAMTIC</t>
+  </si>
+  <si>
     <t>BURUANGA</t>
   </si>
   <si>
@@ -45,9 +54,6 @@
     <t>SIGMA</t>
   </si>
   <si>
-    <t>PILAR</t>
-  </si>
-  <si>
     <t>TUBUNGAN</t>
   </si>
   <si>
@@ -57,6 +63,15 @@
     <t>pull_item</t>
   </si>
   <si>
+    <t>cabbage</t>
+  </si>
+  <si>
+    <t>mango</t>
+  </si>
+  <si>
+    <t>mineral or spring water, all drinking water sold in containers</t>
+  </si>
+  <si>
     <t>beer</t>
   </si>
   <si>
@@ -69,18 +84,21 @@
     <t>liquor (e.g, whisky, coconut wine)</t>
   </si>
   <si>
-    <t>mango</t>
-  </si>
-  <si>
-    <t>mineral or spring water, all drinking water sold in containers</t>
-  </si>
-  <si>
     <t>rice</t>
   </si>
   <si>
     <t>pull_nsu_unit</t>
   </si>
   <si>
+    <t>2 kapinutos nga cabbage/20pesos</t>
+  </si>
+  <si>
+    <t>pieces/ kilo</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
     <t>bottle (500 ml)</t>
   </si>
   <si>
@@ -96,9 +114,6 @@
     <t>bottle of ginebra s. miguel 350ml</t>
   </si>
   <si>
-    <t>pieces/ kilo</t>
-  </si>
-  <si>
     <t>6 liters of water (2 blue container)</t>
   </si>
   <si>
@@ -108,6 +123,15 @@
     <t>1/2 sack of rice (25kls.)</t>
   </si>
   <si>
+    <t>drop_reason</t>
+  </si>
+  <si>
+    <t>ambiguous quantity</t>
+  </si>
+  <si>
+    <t>standard quantity</t>
+  </si>
+  <si>
     <t>weighing_approach</t>
   </si>
   <si>
@@ -126,73 +150,106 @@
     <t>vendor_id</t>
   </si>
   <si>
+    <t>KED6C3DL</t>
+  </si>
+  <si>
+    <t>PTGS9CZB</t>
+  </si>
+  <si>
+    <t>AG60CRCP</t>
+  </si>
+  <si>
+    <t>ANAOAQ31</t>
+  </si>
+  <si>
+    <t>UMOP0H16</t>
+  </si>
+  <si>
+    <t>6IU6X8LE</t>
+  </si>
+  <si>
+    <t>3PQJGPX2</t>
+  </si>
+  <si>
+    <t>7E61LTA6</t>
+  </si>
+  <si>
+    <t>K7QZ5BIX</t>
+  </si>
+  <si>
+    <t>81YD2D4Y</t>
+  </si>
+  <si>
+    <t>UECM6ZZ7</t>
+  </si>
+  <si>
     <t>BHI84A67</t>
   </si>
   <si>
+    <t>86YRLEXE</t>
+  </si>
+  <si>
+    <t>P90EVCOR</t>
+  </si>
+  <si>
     <t>W3Y98A7M</t>
   </si>
   <si>
-    <t>P90EVCOR</t>
-  </si>
-  <si>
-    <t>86YRLEXE</t>
-  </si>
-  <si>
     <t>6SML8FIT</t>
   </si>
   <si>
+    <t>0X6CXPQB</t>
+  </si>
+  <si>
+    <t>B5LXNNSR</t>
+  </si>
+  <si>
     <t>4JW4PL87</t>
   </si>
   <si>
-    <t>0X6CXPQB</t>
-  </si>
-  <si>
-    <t>B5LXNNSR</t>
-  </si>
-  <si>
     <t>PXGODZC7</t>
   </si>
   <si>
     <t>3DCR6LIR</t>
   </si>
   <si>
+    <t>2GQ9D2ZK</t>
+  </si>
+  <si>
+    <t>8E5XGY1Y</t>
+  </si>
+  <si>
     <t>EKKENYZA</t>
   </si>
   <si>
-    <t>2GQ9D2ZK</t>
-  </si>
-  <si>
-    <t>8E5XGY1Y</t>
-  </si>
-  <si>
-    <t>6IU6X8LE</t>
-  </si>
-  <si>
-    <t>UMOP0H16</t>
+    <t>57T6R5X5</t>
+  </si>
+  <si>
+    <t>U3E4WK7B</t>
+  </si>
+  <si>
+    <t>URHLCIO0</t>
   </si>
   <si>
     <t>9B8ZS4PI</t>
   </si>
   <si>
+    <t>WAZ19DZ2</t>
+  </si>
+  <si>
     <t>1RNST8HU</t>
   </si>
   <si>
-    <t>URHLCIO0</t>
-  </si>
-  <si>
-    <t>U3E4WK7B</t>
-  </si>
-  <si>
-    <t>57T6R5X5</t>
+    <t>SU9T7L6Y</t>
   </si>
   <si>
     <t>XO779UU5</t>
   </si>
   <si>
-    <t>WAZ19DZ2</t>
-  </si>
-  <si>
-    <t>SU9T7L6Y</t>
+    <t>9ZZZITD0</t>
+  </si>
+  <si>
+    <t>594IJ96W</t>
   </si>
   <si>
     <t>WGKFP079</t>
@@ -201,12 +258,6 @@
     <t>FK0QULBI</t>
   </si>
   <si>
-    <t>594IJ96W</t>
-  </si>
-  <si>
-    <t>9ZZZITD0</t>
-  </si>
-  <si>
     <t>IL8ZCWTF</t>
   </si>
   <si>
@@ -222,12 +273,12 @@
     <t>grams (g)</t>
   </si>
   <si>
+    <t>Litres (L)</t>
+  </si>
+  <si>
     <t>Kilograms (Kgs)</t>
   </si>
   <si>
-    <t>Litres (L)</t>
-  </si>
-  <si>
     <t>weight</t>
   </si>
   <si>
@@ -243,70 +294,19 @@
     <t>hetero_lbl</t>
   </si>
   <si>
+    <t>small_size</t>
+  </si>
+  <si>
     <t>medium_size</t>
   </si>
   <si>
+    <t>large_size</t>
+  </si>
+  <si>
     <t>province_median</t>
   </si>
   <si>
-    <t>large_size</t>
-  </si>
-  <si>
-    <t>small_size</t>
-  </si>
-  <si>
     <t>conventional_nsu</t>
-  </si>
-  <si>
-    <t>HAMTIC</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>drop_reason</t>
-  </si>
-  <si>
-    <t>ambiguous quantity</t>
-  </si>
-  <si>
-    <t>standard quantity</t>
-  </si>
-  <si>
-    <t>3PQJGPX2</t>
-  </si>
-  <si>
-    <t>81YD2D4Y</t>
-  </si>
-  <si>
-    <t>K7QZ5BIX</t>
-  </si>
-  <si>
-    <t>UECM6ZZ7</t>
-  </si>
-  <si>
-    <t>7E61LTA6</t>
-  </si>
-  <si>
-    <t>DUEAS</t>
-  </si>
-  <si>
-    <t>cabbage</t>
-  </si>
-  <si>
-    <t>2 kapinutos nga cabbage/20pesos</t>
-  </si>
-  <si>
-    <t>KED6C3DL</t>
-  </si>
-  <si>
-    <t>PTGS9CZB</t>
-  </si>
-  <si>
-    <t>AG60CRCP</t>
-  </si>
-  <si>
-    <t>ANAOAQ31</t>
   </si>
 </sst>
 </file>
@@ -363,208 +363,208 @@
         <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" t="s">
         <v>83</v>
       </c>
-      <c r="F1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I1" t="s">
-        <v>66</v>
-      </c>
       <c r="J1" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="K1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="L1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="M1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="N1" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G2" s="1">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K2" s="1">
         <v>330</v>
       </c>
       <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" t="s">
         <v>93</v>
-      </c>
-      <c r="M2" t="s">
-        <v>93</v>
-      </c>
-      <c r="N2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G3" s="1">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K3" s="1">
         <v>235</v>
       </c>
       <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" t="s">
         <v>93</v>
-      </c>
-      <c r="M3" t="s">
-        <v>93</v>
-      </c>
-      <c r="N3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G4" s="1">
         <v>2</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K4" s="1">
         <v>325</v>
       </c>
       <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" t="s">
         <v>93</v>
-      </c>
-      <c r="M4" t="s">
-        <v>93</v>
-      </c>
-      <c r="N4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K5" s="1">
         <v>285</v>
       </c>
       <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
         <v>93</v>
-      </c>
-      <c r="M5" t="s">
-        <v>93</v>
-      </c>
-      <c r="N5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="6">
@@ -572,41 +572,41 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G6" s="1">
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K6" s="1">
         <v>220</v>
       </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -614,41 +614,41 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K7" s="1">
         <v>245</v>
       </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -656,19 +656,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -678,19 +678,19 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K8" s="1">
         <v>0.25999999046325684</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -698,41 +698,41 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G9" s="1">
         <v>2</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K9" s="1">
         <v>170</v>
       </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -740,19 +740,19 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -762,19 +762,19 @@
       </c>
       <c r="I10" s="1"/>
       <c r="J10" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K10" s="1">
         <v>0.2199999988079071</v>
       </c>
       <c r="L10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -782,19 +782,19 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
@@ -804,19 +804,19 @@
       </c>
       <c r="I11" s="1"/>
       <c r="J11" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K11" s="1">
         <v>0.20000000298023224</v>
       </c>
       <c r="L11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -824,41 +824,41 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K12" s="1">
         <v>0.5</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N12" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -866,41 +866,41 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G13" s="1">
         <v>3</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K13" s="1">
         <v>0.5</v>
       </c>
       <c r="L13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N13" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -908,41 +908,41 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1">
         <v>3</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K14" s="1">
         <v>0.5</v>
       </c>
       <c r="L14" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M14" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N14" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -950,41 +950,41 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K15" s="1">
         <v>0.5</v>
       </c>
       <c r="L15" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M15" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N15" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
@@ -992,209 +992,209 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K16" s="1">
         <v>0.5</v>
       </c>
       <c r="L16" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N16" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F17" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G17" s="1">
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K17" s="1">
         <v>500</v>
       </c>
       <c r="L17" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N17" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G18" s="1">
         <v>3</v>
       </c>
       <c r="H18" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K18" s="1">
         <v>500</v>
       </c>
       <c r="L18" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N18" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G19" s="1">
         <v>3</v>
       </c>
       <c r="H19" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K19" s="1">
         <v>500</v>
       </c>
       <c r="L19" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M19" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N19" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1">
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K20" s="1">
         <v>500</v>
       </c>
       <c r="L20" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N20" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21">
@@ -1202,43 +1202,43 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G21" s="1">
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="I21" s="1">
         <v>28.571428298950195</v>
       </c>
       <c r="J21" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K21" s="1">
         <v>190</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N21" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22">
@@ -1246,43 +1246,43 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="I22" s="1">
         <v>28.571428298950195</v>
       </c>
       <c r="J22" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K22" s="1">
         <v>190</v>
       </c>
       <c r="L22" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N22" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23">
@@ -1290,43 +1290,43 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G23" s="1">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="I23" s="1">
         <v>28.571428298950195</v>
       </c>
       <c r="J23" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K23" s="1">
         <v>175</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N23" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24">
@@ -1334,43 +1334,43 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="I24" s="1">
         <v>28.571428298950195</v>
       </c>
       <c r="J24" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K24" s="1">
         <v>250</v>
       </c>
       <c r="L24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M24" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
@@ -1378,41 +1378,41 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G25" s="1">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K25" s="1">
         <v>1.5</v>
       </c>
       <c r="L25" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M25" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26">
@@ -1420,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E26" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G26" s="1">
         <v>3</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="I26" s="1">
         <v>125</v>
       </c>
       <c r="J26" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K26" s="1">
         <v>500</v>
       </c>
       <c r="L26" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M26" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N26" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27">
@@ -1464,41 +1464,41 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K27" s="1">
         <v>350</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N27" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28">
@@ -1506,41 +1506,41 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K28" s="1">
         <v>350</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M28" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N28" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29">
@@ -1548,629 +1548,629 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="K29" s="1">
         <v>350</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N29" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E30" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K30" s="1">
         <v>0.0060000000521540642</v>
       </c>
       <c r="L30" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M30" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N30" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E31" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G31" s="1">
         <v>3</v>
       </c>
       <c r="H31" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K31" s="1">
         <v>0.0065999999642372131</v>
       </c>
       <c r="L31" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M31" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N31" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G32" s="1">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K32" s="1">
         <v>0.0060000000521540642</v>
       </c>
       <c r="L32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M32" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N32" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E33" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G33" s="1">
         <v>3</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K33" s="1">
         <v>21.004999160766602</v>
       </c>
       <c r="L33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M33" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N33" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G34" s="1">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K34" s="1">
         <v>6</v>
       </c>
       <c r="L34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M34" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N34" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G35" s="1">
         <v>3</v>
       </c>
       <c r="H35" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K35" s="1">
         <v>0.0060000000521540642</v>
       </c>
       <c r="L35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M35" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N35" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E36" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K36" s="1">
         <v>21.670000076293945</v>
       </c>
       <c r="L36" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M36" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N36" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G37" s="1">
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K37" s="1">
         <v>21.479999542236328</v>
       </c>
       <c r="L37" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M37" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="N37" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F38" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G38" s="1">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K38" s="1">
         <v>0.0099999997764825821</v>
       </c>
       <c r="L38" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M38" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N38" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G39" s="1">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K39" s="1">
         <v>0.0099999997764825821</v>
       </c>
       <c r="L39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M39" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N39" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G40" s="1">
         <v>3</v>
       </c>
       <c r="H40" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K40" s="1">
         <v>0.0099999997764825821</v>
       </c>
       <c r="L40" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M40" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N40" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F41" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G41" s="1">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="K41" s="1">
         <v>0.0099999997764825821</v>
       </c>
       <c r="L41" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M41" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="N41" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K42" s="1">
         <v>25</v>
       </c>
       <c r="L42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N42" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F43" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="K43" s="1">
         <v>25</v>
       </c>
       <c r="L43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="N43" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="476" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1428" uniqueCount="98">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1428" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2380" uniqueCount="98">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2380" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2856" uniqueCount="98">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2856" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3332" uniqueCount="98">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3332" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4284" uniqueCount="98">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4284" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="9748" uniqueCount="126">
   <si>
     <t>pull_province</t>
   </si>
@@ -307,6 +307,90 @@
   </si>
   <si>
     <t>conventional_nsu</t>
+  </si>
+  <si>
+    <t>MA-AYON</t>
+  </si>
+  <si>
+    <t>ANILAO</t>
+  </si>
+  <si>
+    <t>SAN MIGUEL</t>
+  </si>
+  <si>
+    <t>BADIANGAN</t>
+  </si>
+  <si>
+    <t>ice cream, sorbet, edible ice (eg., ice-lolli, halo-halo)</t>
+  </si>
+  <si>
+    <t>3 for 25 pesos (putos)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>pack 25 per pack in the market</t>
+  </si>
+  <si>
+    <t>1.3 galon</t>
+  </si>
+  <si>
+    <t>6 bottles of redhorse</t>
+  </si>
+  <si>
+    <t>not a unit</t>
+  </si>
+  <si>
+    <t>GDTVNFV5</t>
+  </si>
+  <si>
+    <t>HG2R8UR3</t>
+  </si>
+  <si>
+    <t>O6NGCL26</t>
+  </si>
+  <si>
+    <t>S35CS7NJ</t>
+  </si>
+  <si>
+    <t>I8GEW5EU</t>
+  </si>
+  <si>
+    <t>SXMR65WI</t>
+  </si>
+  <si>
+    <t>BF1CVWI7</t>
+  </si>
+  <si>
+    <t>REYDZ29A</t>
+  </si>
+  <si>
+    <t>3IJHQ24N</t>
+  </si>
+  <si>
+    <t>CUANELG7</t>
+  </si>
+  <si>
+    <t>MY7HILN0</t>
+  </si>
+  <si>
+    <t>XV2VXESL</t>
+  </si>
+  <si>
+    <t>CUHOQ9ZL</t>
+  </si>
+  <si>
+    <t>TOWN43MQ</t>
+  </si>
+  <si>
+    <t>C4XJTQ65</t>
+  </si>
+  <si>
+    <t>DR4X8J9Z</t>
+  </si>
+  <si>
+    <t>1.3 gallon</t>
   </si>
 </sst>
 </file>
@@ -352,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +587,17 @@
         <v>40</v>
       </c>
       <c r="G4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" t="s">
         <v>85</v>
       </c>
       <c r="K4" s="1">
-        <v>325</v>
+        <v>285</v>
       </c>
       <c r="L4" t="s">
         <v>25</v>
@@ -545,17 +629,17 @@
         <v>40</v>
       </c>
       <c r="G5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" t="s">
         <v>85</v>
       </c>
       <c r="K5" s="1">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="L5" t="s">
         <v>25</v>
@@ -569,16 +653,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -587,40 +671,40 @@
         <v>40</v>
       </c>
       <c r="G6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" t="s">
         <v>85</v>
       </c>
       <c r="K6" s="1">
-        <v>220</v>
+        <v>395</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="N6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>37</v>
@@ -629,40 +713,40 @@
         <v>40</v>
       </c>
       <c r="G7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" t="s">
         <v>85</v>
       </c>
       <c r="K7" s="1">
-        <v>245</v>
+        <v>495</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="N7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>37</v>
@@ -671,40 +755,40 @@
         <v>40</v>
       </c>
       <c r="G8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" t="s">
         <v>85</v>
       </c>
       <c r="K8" s="1">
-        <v>0.25999999046325684</v>
+        <v>485</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="N8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>37</v>
@@ -713,23 +797,23 @@
         <v>40</v>
       </c>
       <c r="G9" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" t="s">
         <v>85</v>
       </c>
       <c r="K9" s="1">
-        <v>170</v>
+        <v>400</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="N9" t="s">
         <v>93</v>
@@ -740,41 +824,43 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
         <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="1"/>
+        <v>113</v>
+      </c>
+      <c r="I10" s="1">
+        <v>20</v>
+      </c>
       <c r="J10" t="s">
         <v>85</v>
       </c>
       <c r="K10" s="1">
-        <v>0.2199999988079071</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="M10" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="N10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -782,97 +868,101 @@
         <v>2</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
         <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" s="1">
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="I11" s="1">
+        <v>20</v>
+      </c>
       <c r="J11" t="s">
         <v>85</v>
       </c>
       <c r="K11" s="1">
-        <v>0.20000000298023224</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="N11" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1">
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="I12" s="1">
+        <v>20</v>
+      </c>
       <c r="J12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K12" s="1">
-        <v>0.5</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="M12" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="N12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
         <v>37</v>
@@ -881,23 +971,23 @@
         <v>40</v>
       </c>
       <c r="G13" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K13" s="1">
-        <v>0.5</v>
+        <v>220</v>
       </c>
       <c r="L13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M13" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="N13" t="s">
         <v>94</v>
@@ -905,16 +995,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
         <v>37</v>
@@ -923,40 +1013,40 @@
         <v>40</v>
       </c>
       <c r="G14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K14" s="1">
-        <v>0.5</v>
+        <v>245</v>
       </c>
       <c r="L14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -965,40 +1055,40 @@
         <v>40</v>
       </c>
       <c r="G15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K15" s="1">
-        <v>0.5</v>
+        <v>0.20000000298023224</v>
       </c>
       <c r="L15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
@@ -1007,23 +1097,23 @@
         <v>40</v>
       </c>
       <c r="G16" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K16" s="1">
-        <v>0.5</v>
+        <v>0.2199999988079071</v>
       </c>
       <c r="L16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M16" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="N16" t="s">
         <v>94</v>
@@ -1031,19 +1121,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F17" t="s">
         <v>40</v>
@@ -1052,98 +1142,98 @@
         <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" t="s">
         <v>85</v>
       </c>
       <c r="K17" s="1">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="L17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F18" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" t="s">
         <v>85</v>
       </c>
       <c r="K18" s="1">
-        <v>500</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="L18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
         <v>40</v>
       </c>
       <c r="G19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K19" s="1">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="L19" t="s">
         <v>28</v>
@@ -1157,19 +1247,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F20" t="s">
         <v>40</v>
@@ -1178,14 +1268,14 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K20" s="1">
-        <v>500</v>
+        <v>0.5</v>
       </c>
       <c r="L20" t="s">
         <v>28</v>
@@ -1199,151 +1289,145 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G21" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="1">
-        <v>28.571428298950195</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I21" s="1"/>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K21" s="1">
-        <v>190</v>
+        <v>0.5</v>
       </c>
       <c r="L21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M21" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="N21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
-      </c>
-      <c r="I22" s="1">
-        <v>28.571428298950195</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="I22" s="1"/>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K22" s="1">
-        <v>190</v>
+        <v>0.5</v>
       </c>
       <c r="L22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M22" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="N22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>62</v>
-      </c>
-      <c r="I23" s="1">
-        <v>28.571428298950195</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="I23" s="1"/>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K23" s="1">
-        <v>175</v>
+        <v>0.5</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M23" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="N23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="E24" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F24" t="s">
         <v>41</v>
@@ -1352,22 +1436,22 @@
         <v>3</v>
       </c>
       <c r="H24" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="I24" s="1">
-        <v>28.571428298950195</v>
+        <v>25</v>
       </c>
       <c r="J24" t="s">
         <v>85</v>
       </c>
       <c r="K24" s="1">
-        <v>250</v>
+        <v>0.38499999046325684</v>
       </c>
       <c r="L24" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="M24" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="N24" t="s">
         <v>96</v>
@@ -1375,85 +1459,87 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="1">
         <v>3</v>
       </c>
-      <c r="B25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1</v>
-      </c>
       <c r="H25" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="1"/>
+        <v>117</v>
+      </c>
+      <c r="I25" s="1">
+        <v>25</v>
+      </c>
       <c r="J25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K25" s="1">
-        <v>1.5</v>
+        <v>300</v>
       </c>
       <c r="L25" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="M25" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="N25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F26" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="I26" s="1">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K26" s="1">
-        <v>500</v>
+        <v>0.28999999165534973</v>
       </c>
       <c r="L26" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="M26" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="N26" t="s">
         <v>96</v>
@@ -1461,100 +1547,104 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" s="1"/>
+        <v>119</v>
+      </c>
+      <c r="I27" s="1">
+        <v>25</v>
+      </c>
       <c r="J27" t="s">
         <v>85</v>
       </c>
       <c r="K27" s="1">
-        <v>350</v>
+        <v>0.27500000596046448</v>
       </c>
       <c r="L27" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="N27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G28" s="1">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>67</v>
-      </c>
-      <c r="I28" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="I28" s="1">
+        <v>25</v>
+      </c>
       <c r="J28" t="s">
         <v>85</v>
       </c>
       <c r="K28" s="1">
-        <v>350</v>
+        <v>0.28499999642372131</v>
       </c>
       <c r="L28" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="M28" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="N28" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E29" t="s">
         <v>38</v>
@@ -1563,40 +1653,40 @@
         <v>40</v>
       </c>
       <c r="G29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" t="s">
         <v>85</v>
       </c>
       <c r="K29" s="1">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="L29" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="M29" t="s">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="N29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
         <v>38</v>
@@ -1605,40 +1695,40 @@
         <v>40</v>
       </c>
       <c r="G30" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K30" s="1">
-        <v>0.0060000000521540642</v>
+        <v>500</v>
       </c>
       <c r="L30" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M30" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="N30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E31" t="s">
         <v>38</v>
@@ -1650,20 +1740,20 @@
         <v>3</v>
       </c>
       <c r="H31" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K31" s="1">
-        <v>0.0065999999642372131</v>
+        <v>500</v>
       </c>
       <c r="L31" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M31" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="N31" t="s">
         <v>94</v>
@@ -1671,16 +1761,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E32" t="s">
         <v>38</v>
@@ -1689,208 +1779,216 @@
         <v>40</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K32" s="1">
-        <v>0.0060000000521540642</v>
+        <v>500</v>
       </c>
       <c r="L32" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="M32" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="N32" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E33" t="s">
         <v>38</v>
       </c>
       <c r="F33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G33" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
-      </c>
-      <c r="I33" s="1"/>
+        <v>61</v>
+      </c>
+      <c r="I33" s="1">
+        <v>28.571428298950195</v>
+      </c>
       <c r="J33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K33" s="1">
-        <v>21.004999160766602</v>
+        <v>190</v>
       </c>
       <c r="L33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M33" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E34" t="s">
         <v>38</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" t="s">
-        <v>73</v>
-      </c>
-      <c r="I34" s="1"/>
+        <v>63</v>
+      </c>
+      <c r="I34" s="1">
+        <v>28.571428298950195</v>
+      </c>
       <c r="J34" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K34" s="1">
-        <v>6</v>
+        <v>250</v>
       </c>
       <c r="L34" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M34" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N34" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E35" t="s">
         <v>38</v>
       </c>
       <c r="F35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G35" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>74</v>
-      </c>
-      <c r="I35" s="1"/>
+        <v>62</v>
+      </c>
+      <c r="I35" s="1">
+        <v>28.571428298950195</v>
+      </c>
       <c r="J35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K35" s="1">
-        <v>0.0060000000521540642</v>
+        <v>175</v>
       </c>
       <c r="L35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M35" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N35" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
         <v>38</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G36" s="1">
         <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>75</v>
-      </c>
-      <c r="I36" s="1"/>
+        <v>60</v>
+      </c>
+      <c r="I36" s="1">
+        <v>28.571428298950195</v>
+      </c>
       <c r="J36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K36" s="1">
-        <v>21.670000076293945</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M36" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N36" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E37" t="s">
         <v>38</v>
@@ -1899,26 +1997,26 @@
         <v>40</v>
       </c>
       <c r="G37" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" t="s">
         <v>87</v>
       </c>
       <c r="K37" s="1">
-        <v>21.479999542236328</v>
+        <v>1.5</v>
       </c>
       <c r="L37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="M37" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38">
@@ -1926,13 +2024,13 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
         <v>38</v>
@@ -1944,20 +2042,20 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" t="s">
         <v>86</v>
       </c>
       <c r="K38" s="1">
-        <v>0.0099999997764825821</v>
+        <v>0.0013000000035390258</v>
       </c>
       <c r="L38" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="M38" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="N38" t="s">
         <v>95</v>
@@ -1965,44 +2063,46 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
       </c>
       <c r="F39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39" t="s">
-        <v>78</v>
-      </c>
-      <c r="I39" s="1"/>
+        <v>65</v>
+      </c>
+      <c r="I39" s="1">
+        <v>125</v>
+      </c>
       <c r="J39" t="s">
         <v>86</v>
       </c>
       <c r="K39" s="1">
-        <v>0.0099999997764825821</v>
+        <v>500</v>
       </c>
       <c r="L39" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M39" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="N39" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40">
@@ -2010,13 +2110,13 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="E40" t="s">
         <v>38</v>
@@ -2025,26 +2125,26 @@
         <v>40</v>
       </c>
       <c r="G40" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K40" s="1">
-        <v>0.0099999997764825821</v>
+        <v>500</v>
       </c>
       <c r="L40" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="M40" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="N40" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41">
@@ -2052,13 +2152,13 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="E41" t="s">
         <v>38</v>
@@ -2070,23 +2170,23 @@
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>80</v>
+        <v>123</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K41" s="1">
-        <v>0.0099999997764825821</v>
+        <v>330</v>
       </c>
       <c r="L41" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="M41" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="N41" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42">
@@ -2094,82 +2194,754 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D42" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="E42" t="s">
         <v>38</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G42" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K42" s="1">
-        <v>25</v>
+        <v>330</v>
       </c>
       <c r="L42" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="M42" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="N42" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E43" t="s">
         <v>38</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G43" s="1">
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" t="s">
+        <v>85</v>
+      </c>
+      <c r="K43" s="1">
+        <v>350</v>
+      </c>
+      <c r="L43" t="s">
+        <v>32</v>
+      </c>
+      <c r="M43" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D44" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" t="s">
+        <v>40</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" t="s">
+        <v>67</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" t="s">
+        <v>85</v>
+      </c>
+      <c r="K44" s="1">
+        <v>350</v>
+      </c>
+      <c r="L44" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" t="s">
+        <v>32</v>
+      </c>
+      <c r="N44" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" t="s">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s">
+        <v>38</v>
+      </c>
+      <c r="F45" t="s">
+        <v>40</v>
+      </c>
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>66</v>
+      </c>
+      <c r="I45" s="1"/>
+      <c r="J45" t="s">
+        <v>85</v>
+      </c>
+      <c r="K45" s="1">
+        <v>350</v>
+      </c>
+      <c r="L45" t="s">
+        <v>32</v>
+      </c>
+      <c r="M45" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" t="s">
+        <v>33</v>
+      </c>
+      <c r="E46" t="s">
+        <v>38</v>
+      </c>
+      <c r="F46" t="s">
+        <v>40</v>
+      </c>
+      <c r="G46" s="1">
+        <v>3</v>
+      </c>
+      <c r="H46" t="s">
+        <v>70</v>
+      </c>
+      <c r="I46" s="1"/>
+      <c r="J46" t="s">
+        <v>86</v>
+      </c>
+      <c r="K46" s="1">
+        <v>0.0065999999642372131</v>
+      </c>
+      <c r="L46" t="s">
+        <v>33</v>
+      </c>
+      <c r="M46" t="s">
+        <v>33</v>
+      </c>
+      <c r="N46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>1</v>
+      </c>
+      <c r="B47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" t="s">
+        <v>38</v>
+      </c>
+      <c r="F47" t="s">
+        <v>40</v>
+      </c>
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="1"/>
+      <c r="J47" t="s">
+        <v>86</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0.0060000000521540642</v>
+      </c>
+      <c r="L47" t="s">
+        <v>33</v>
+      </c>
+      <c r="M47" t="s">
+        <v>33</v>
+      </c>
+      <c r="N47" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" t="s">
+        <v>38</v>
+      </c>
+      <c r="F48" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="1">
+        <v>3</v>
+      </c>
+      <c r="H48" t="s">
+        <v>74</v>
+      </c>
+      <c r="I48" s="1"/>
+      <c r="J48" t="s">
+        <v>86</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0.0060000000521540642</v>
+      </c>
+      <c r="L48" t="s">
+        <v>33</v>
+      </c>
+      <c r="M48" t="s">
+        <v>33</v>
+      </c>
+      <c r="N48" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" t="s">
+        <v>40</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" t="s">
+        <v>69</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" t="s">
+        <v>86</v>
+      </c>
+      <c r="K49" s="1">
+        <v>0.0060000000521540642</v>
+      </c>
+      <c r="L49" t="s">
+        <v>33</v>
+      </c>
+      <c r="M49" t="s">
+        <v>33</v>
+      </c>
+      <c r="N49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>1</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" t="s">
+        <v>33</v>
+      </c>
+      <c r="E50" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" t="s">
+        <v>40</v>
+      </c>
+      <c r="G50" s="1">
+        <v>2</v>
+      </c>
+      <c r="H50" t="s">
+        <v>76</v>
+      </c>
+      <c r="I50" s="1"/>
+      <c r="J50" t="s">
         <v>87</v>
       </c>
-      <c r="K43" s="1">
+      <c r="K50" s="1">
+        <v>21.479999542236328</v>
+      </c>
+      <c r="L50" t="s">
+        <v>33</v>
+      </c>
+      <c r="M50" t="s">
+        <v>33</v>
+      </c>
+      <c r="N50" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" t="s">
+        <v>38</v>
+      </c>
+      <c r="F51" t="s">
+        <v>40</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" t="s">
+        <v>75</v>
+      </c>
+      <c r="I51" s="1"/>
+      <c r="J51" t="s">
+        <v>87</v>
+      </c>
+      <c r="K51" s="1">
+        <v>21.670000076293945</v>
+      </c>
+      <c r="L51" t="s">
+        <v>33</v>
+      </c>
+      <c r="M51" t="s">
+        <v>33</v>
+      </c>
+      <c r="N51" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" t="s">
+        <v>38</v>
+      </c>
+      <c r="F52" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" s="1">
+        <v>3</v>
+      </c>
+      <c r="H52" t="s">
+        <v>72</v>
+      </c>
+      <c r="I52" s="1"/>
+      <c r="J52" t="s">
+        <v>87</v>
+      </c>
+      <c r="K52" s="1">
+        <v>21.004999160766602</v>
+      </c>
+      <c r="L52" t="s">
+        <v>33</v>
+      </c>
+      <c r="M52" t="s">
+        <v>33</v>
+      </c>
+      <c r="N52" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" t="s">
+        <v>38</v>
+      </c>
+      <c r="F53" t="s">
+        <v>40</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>73</v>
+      </c>
+      <c r="I53" s="1"/>
+      <c r="J53" t="s">
+        <v>86</v>
+      </c>
+      <c r="K53" s="1">
+        <v>6</v>
+      </c>
+      <c r="L53" t="s">
+        <v>33</v>
+      </c>
+      <c r="M53" t="s">
+        <v>33</v>
+      </c>
+      <c r="N53" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" t="s">
+        <v>38</v>
+      </c>
+      <c r="F54" t="s">
+        <v>40</v>
+      </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
+      <c r="H54" t="s">
+        <v>78</v>
+      </c>
+      <c r="I54" s="1"/>
+      <c r="J54" t="s">
+        <v>86</v>
+      </c>
+      <c r="K54" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L54" t="s">
+        <v>34</v>
+      </c>
+      <c r="M54" t="s">
+        <v>34</v>
+      </c>
+      <c r="N54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" t="s">
+        <v>34</v>
+      </c>
+      <c r="E55" t="s">
+        <v>38</v>
+      </c>
+      <c r="F55" t="s">
+        <v>40</v>
+      </c>
+      <c r="G55" s="1">
+        <v>3</v>
+      </c>
+      <c r="H55" t="s">
+        <v>79</v>
+      </c>
+      <c r="I55" s="1"/>
+      <c r="J55" t="s">
+        <v>86</v>
+      </c>
+      <c r="K55" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L55" t="s">
+        <v>34</v>
+      </c>
+      <c r="M55" t="s">
+        <v>34</v>
+      </c>
+      <c r="N55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56" t="s">
+        <v>38</v>
+      </c>
+      <c r="F56" t="s">
+        <v>40</v>
+      </c>
+      <c r="G56" s="1">
+        <v>1</v>
+      </c>
+      <c r="H56" t="s">
+        <v>80</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" t="s">
+        <v>86</v>
+      </c>
+      <c r="K56" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L56" t="s">
+        <v>34</v>
+      </c>
+      <c r="M56" t="s">
+        <v>34</v>
+      </c>
+      <c r="N56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>1</v>
+      </c>
+      <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" t="s">
+        <v>34</v>
+      </c>
+      <c r="E57" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" t="s">
+        <v>40</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" t="s">
+        <v>77</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" t="s">
+        <v>86</v>
+      </c>
+      <c r="K57" s="1">
+        <v>0.0099999997764825821</v>
+      </c>
+      <c r="L57" t="s">
+        <v>34</v>
+      </c>
+      <c r="M57" t="s">
+        <v>34</v>
+      </c>
+      <c r="N57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" t="s">
+        <v>38</v>
+      </c>
+      <c r="F58" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="1">
+        <v>1</v>
+      </c>
+      <c r="H58" t="s">
+        <v>81</v>
+      </c>
+      <c r="I58" s="1"/>
+      <c r="J58" t="s">
+        <v>87</v>
+      </c>
+      <c r="K58" s="1">
         <v>25</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L58" t="s">
         <v>35</v>
       </c>
-      <c r="M43" t="s">
+      <c r="M58" t="s">
         <v>35</v>
       </c>
-      <c r="N43" t="s">
+      <c r="N58" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>35</v>
+      </c>
+      <c r="E59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" s="1">
+        <v>1</v>
+      </c>
+      <c r="H59" t="s">
+        <v>82</v>
+      </c>
+      <c r="I59" s="1"/>
+      <c r="J59" t="s">
+        <v>87</v>
+      </c>
+      <c r="K59" s="1">
+        <v>25</v>
+      </c>
+      <c r="L59" t="s">
+        <v>35</v>
+      </c>
+      <c r="M59" t="s">
+        <v>35</v>
+      </c>
+      <c r="N59" t="s">
         <v>97</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="9748" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10400" uniqueCount="126">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="10400" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11052" uniqueCount="126">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11052" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11704" uniqueCount="126">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="11704" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="13660" uniqueCount="126">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="13660" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="14965" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>
@@ -391,6 +391,9 @@
   </si>
   <si>
     <t>1.3 gallon</t>
+  </si>
+  <si>
+    <t>id</t>
   </si>
 </sst>
 </file>
@@ -436,2512 +439,2689 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:O59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>24</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>44</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>83</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>84</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>88</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>89</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>90</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
-        <v>1</v>
+      <c r="A2" s="1">
+        <v>6756</v>
       </c>
       <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>37</v>
       </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K2" s="1">
-        <v>330</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="1">
+        <v>285</v>
       </c>
       <c r="M2" t="s">
         <v>25</v>
       </c>
       <c r="N2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
-        <v>1</v>
+      <c r="A3" s="1">
+        <v>6755</v>
       </c>
       <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>37</v>
       </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" s="1">
-        <v>235</v>
-      </c>
-      <c r="L3" t="s">
-        <v>25</v>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="1">
+        <v>2</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" t="s">
+        <v>85</v>
+      </c>
+      <c r="L3" s="1">
+        <v>325</v>
       </c>
       <c r="M3" t="s">
         <v>25</v>
       </c>
       <c r="N3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
-        <v>1</v>
+      <c r="A4" s="1">
+        <v>6757</v>
       </c>
       <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" s="1"/>
-      <c r="J4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="1">
-        <v>285</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4" s="1">
+        <v>330</v>
       </c>
       <c r="M4" t="s">
         <v>25</v>
       </c>
       <c r="N4" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>6758</v>
       </c>
       <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>37</v>
       </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="1"/>
-      <c r="J5" t="s">
-        <v>85</v>
-      </c>
-      <c r="K5" s="1">
-        <v>325</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" t="s">
+        <v>85</v>
+      </c>
+      <c r="L5" s="1">
+        <v>235</v>
       </c>
       <c r="M5" t="s">
         <v>25</v>
       </c>
       <c r="N5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>1</v>
+      <c r="A6" s="1">
+        <v>6761</v>
       </c>
       <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>103</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>37</v>
       </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>109</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K6" s="1">
-        <v>395</v>
-      </c>
-      <c r="L6" t="s">
-        <v>103</v>
+      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" t="s">
+        <v>85</v>
+      </c>
+      <c r="L6" s="1">
+        <v>485</v>
       </c>
       <c r="M6" t="s">
         <v>103</v>
       </c>
       <c r="N6" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>1</v>
+      <c r="A7" s="1">
+        <v>6759</v>
       </c>
       <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>103</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" t="s">
-        <v>85</v>
-      </c>
-      <c r="K7" s="1">
-        <v>495</v>
-      </c>
-      <c r="L7" t="s">
-        <v>103</v>
+      <c r="G7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" t="s">
+        <v>85</v>
+      </c>
+      <c r="L7" s="1">
+        <v>395</v>
       </c>
       <c r="M7" t="s">
         <v>103</v>
       </c>
       <c r="N7" t="s">
+        <v>103</v>
+      </c>
+      <c r="O7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>1</v>
+      <c r="A8" s="1">
+        <v>6760</v>
       </c>
       <c r="B8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>103</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>37</v>
       </c>
-      <c r="F8" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
-      </c>
-      <c r="H8" t="s">
-        <v>111</v>
-      </c>
-      <c r="I8" s="1"/>
-      <c r="J8" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="1">
-        <v>485</v>
-      </c>
-      <c r="L8" t="s">
-        <v>103</v>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>110</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="1">
+        <v>495</v>
       </c>
       <c r="M8" t="s">
         <v>103</v>
       </c>
       <c r="N8" t="s">
+        <v>103</v>
+      </c>
+      <c r="O8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>1</v>
+      <c r="A9" s="1">
+        <v>6762</v>
       </c>
       <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>103</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>37</v>
       </c>
-      <c r="F9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G9" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="J9" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="J9" s="1"/>
+      <c r="K9" t="s">
+        <v>85</v>
+      </c>
+      <c r="L9" s="1">
         <v>400</v>
-      </c>
-      <c r="L9" t="s">
-        <v>103</v>
       </c>
       <c r="M9" t="s">
         <v>103</v>
       </c>
       <c r="N9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" s="1">
+        <v>4044</v>
+      </c>
+      <c r="B10" t="s">
         <v>2</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>98</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>104</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>37</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>114</v>
+      </c>
+      <c r="J10" s="1">
         <v>20</v>
       </c>
-      <c r="J10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="1">
-        <v>125</v>
-      </c>
-      <c r="L10" t="s">
-        <v>104</v>
+      <c r="K10" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="1">
+        <v>145</v>
       </c>
       <c r="M10" t="s">
         <v>104</v>
       </c>
       <c r="N10" t="s">
+        <v>104</v>
+      </c>
+      <c r="O10" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s">
+      <c r="A11" s="1">
+        <v>4043</v>
+      </c>
+      <c r="B11" t="s">
         <v>2</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>98</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>20</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>104</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>114</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J11" s="1">
         <v>20</v>
       </c>
-      <c r="J11" t="s">
-        <v>85</v>
-      </c>
-      <c r="K11" s="1">
-        <v>145</v>
-      </c>
-      <c r="L11" t="s">
-        <v>104</v>
+      <c r="K11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L11" s="1">
+        <v>125</v>
       </c>
       <c r="M11" t="s">
         <v>104</v>
       </c>
       <c r="N11" t="s">
+        <v>104</v>
+      </c>
+      <c r="O11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" s="1">
+        <v>4042</v>
+      </c>
+      <c r="B12" t="s">
         <v>2</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>98</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>20</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>104</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>37</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>20</v>
       </c>
-      <c r="J12" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" s="1">
+      <c r="K12" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="1">
         <v>150</v>
-      </c>
-      <c r="L12" t="s">
-        <v>104</v>
       </c>
       <c r="M12" t="s">
         <v>104</v>
       </c>
       <c r="N12" t="s">
+        <v>104</v>
+      </c>
+      <c r="O12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s">
+      <c r="A13" s="1">
+        <v>4634</v>
+      </c>
+      <c r="B13" t="s">
         <v>2</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>17</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>26</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>37</v>
       </c>
-      <c r="F13" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="1">
-        <v>2</v>
-      </c>
-      <c r="H13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" t="s">
-        <v>85</v>
-      </c>
-      <c r="K13" s="1">
-        <v>220</v>
-      </c>
-      <c r="L13" t="s">
-        <v>26</v>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>50</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" t="s">
+        <v>85</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0.25999999046325684</v>
       </c>
       <c r="M13" t="s">
         <v>26</v>
       </c>
       <c r="N13" t="s">
-        <v>94</v>
+        <v>26</v>
+      </c>
+      <c r="O13" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s">
+      <c r="A14" s="1">
+        <v>4636</v>
+      </c>
+      <c r="B14" t="s">
         <v>2</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>7</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>17</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>26</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>37</v>
       </c>
-      <c r="F14" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="1">
+      <c r="G14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="1">
         <v>2</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K14" s="1">
-        <v>245</v>
-      </c>
-      <c r="L14" t="s">
-        <v>26</v>
+      <c r="J14" s="1"/>
+      <c r="K14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="1">
+        <v>220</v>
       </c>
       <c r="M14" t="s">
         <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>26</v>
+      </c>
+      <c r="O14" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
+      <c r="A15" s="1">
+        <v>4635</v>
+      </c>
+      <c r="B15" t="s">
         <v>2</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>7</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>17</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>26</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>37</v>
       </c>
-      <c r="F15" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" t="s">
-        <v>85</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="L15" t="s">
-        <v>26</v>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" s="1">
+        <v>170</v>
       </c>
       <c r="M15" t="s">
         <v>26</v>
       </c>
       <c r="N15" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
+      <c r="A16" s="1">
+        <v>4633</v>
+      </c>
+      <c r="B16" t="s">
         <v>2</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>7</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>26</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>37</v>
       </c>
-      <c r="F16" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
         <v>50</v>
       </c>
-      <c r="I16" s="1"/>
-      <c r="J16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="J16" s="1"/>
+      <c r="K16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L16" s="1">
         <v>0.2199999988079071</v>
-      </c>
-      <c r="L16" t="s">
-        <v>26</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
       </c>
       <c r="N16" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
+      <c r="A17" s="1">
+        <v>4632</v>
+      </c>
+      <c r="B17" t="s">
         <v>2</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>7</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>17</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>37</v>
       </c>
-      <c r="F17" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2</v>
-      </c>
-      <c r="H17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" s="1">
-        <v>170</v>
-      </c>
-      <c r="L17" t="s">
-        <v>26</v>
+      <c r="G17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0.20000000298023224</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
       </c>
       <c r="N17" t="s">
+        <v>26</v>
+      </c>
+      <c r="O17" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
+      <c r="A18" s="1">
+        <v>4637</v>
+      </c>
+      <c r="B18" t="s">
         <v>2</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>26</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>37</v>
       </c>
-      <c r="F18" t="s">
-        <v>40</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>50</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" t="s">
-        <v>85</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0.25999999046325684</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+      <c r="I18" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" t="s">
+        <v>85</v>
+      </c>
+      <c r="L18" s="1">
+        <v>245</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
       </c>
       <c r="N18" t="s">
+        <v>26</v>
+      </c>
+      <c r="O18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s">
+      <c r="A19" s="1">
+        <v>2330</v>
+      </c>
+      <c r="B19" t="s">
         <v>3</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>8</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>27</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>37</v>
       </c>
-      <c r="F19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>54</v>
       </c>
-      <c r="I19" s="1"/>
-      <c r="J19" t="s">
+      <c r="J19" s="1"/>
+      <c r="K19" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>0.5</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>28</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>91</v>
       </c>
-      <c r="N19" t="s">
+      <c r="O19" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s">
+      <c r="A20" s="1">
+        <v>2329</v>
+      </c>
+      <c r="B20" t="s">
         <v>3</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>8</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>18</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>27</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>37</v>
       </c>
-      <c r="F20" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="G20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="1">
         <v>3</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
+        <v>52</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M20" t="s">
+        <v>28</v>
+      </c>
+      <c r="N20" t="s">
+        <v>91</v>
+      </c>
+      <c r="O20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>2328</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" t="s">
+        <v>86</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="M21" t="s">
+        <v>28</v>
+      </c>
+      <c r="N21" t="s">
+        <v>91</v>
+      </c>
+      <c r="O21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1">
+        <v>2331</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="1">
+        <v>3</v>
+      </c>
+      <c r="I22" t="s">
         <v>53</v>
       </c>
-      <c r="I20" s="1"/>
-      <c r="J20" t="s">
+      <c r="J22" s="1"/>
+      <c r="K22" t="s">
         <v>86</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L22" s="1">
         <v>0.5</v>
       </c>
-      <c r="L20" t="s">
+      <c r="M22" t="s">
         <v>28</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N22" t="s">
         <v>91</v>
       </c>
-      <c r="N20" t="s">
+      <c r="O22" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="s">
+    <row r="23">
+      <c r="A23" s="1">
+        <v>2332</v>
+      </c>
+      <c r="B23" t="s">
         <v>3</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C23" t="s">
         <v>8</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D23" t="s">
         <v>18</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E23" t="s">
         <v>27</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F23" t="s">
         <v>37</v>
       </c>
-      <c r="F21" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="1">
+      <c r="G23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H23" s="1">
         <v>3</v>
       </c>
-      <c r="H21" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="1"/>
-      <c r="J21" t="s">
+      <c r="I23" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L23" s="1">
         <v>0.5</v>
       </c>
-      <c r="L21" t="s">
+      <c r="M23" t="s">
         <v>28</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N23" t="s">
         <v>91</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O23" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" t="s">
-        <v>37</v>
-      </c>
-      <c r="F22" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" s="1"/>
-      <c r="J22" t="s">
-        <v>86</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="L22" t="s">
-        <v>28</v>
-      </c>
-      <c r="M22" t="s">
-        <v>91</v>
-      </c>
-      <c r="N22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="1">
-        <v>3</v>
-      </c>
-      <c r="H23" t="s">
-        <v>55</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" t="s">
-        <v>86</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="L23" t="s">
-        <v>28</v>
-      </c>
-      <c r="M23" t="s">
-        <v>91</v>
-      </c>
-      <c r="N23" t="s">
-        <v>94</v>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" t="s">
-        <v>1</v>
+      <c r="A24" s="1">
+        <v>5319</v>
       </c>
       <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>99</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>16</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>105</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>108</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="1">
-        <v>3</v>
-      </c>
-      <c r="H24" t="s">
-        <v>116</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>119</v>
+      </c>
+      <c r="J24" s="1">
         <v>25</v>
       </c>
-      <c r="J24" t="s">
-        <v>85</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0.38499999046325684</v>
-      </c>
-      <c r="L24" t="s">
-        <v>105</v>
+      <c r="K24" t="s">
+        <v>85</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0.27500000596046448</v>
       </c>
       <c r="M24" t="s">
         <v>105</v>
       </c>
       <c r="N24" t="s">
+        <v>105</v>
+      </c>
+      <c r="O24" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s">
-        <v>1</v>
+      <c r="A25" s="1">
+        <v>5321</v>
       </c>
       <c r="B25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>99</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>16</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>105</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>108</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="1">
-        <v>3</v>
-      </c>
-      <c r="H25" t="s">
-        <v>117</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>120</v>
+      </c>
+      <c r="J25" s="1">
         <v>25</v>
       </c>
-      <c r="J25" t="s">
-        <v>85</v>
-      </c>
-      <c r="K25" s="1">
-        <v>300</v>
-      </c>
-      <c r="L25" t="s">
-        <v>105</v>
+      <c r="K25" t="s">
+        <v>85</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0.28499999642372131</v>
       </c>
       <c r="M25" t="s">
         <v>105</v>
       </c>
       <c r="N25" t="s">
+        <v>105</v>
+      </c>
+      <c r="O25" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
-        <v>1</v>
+      <c r="A26" s="1">
+        <v>5320</v>
       </c>
       <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
         <v>99</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>16</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>105</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>108</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>41</v>
       </c>
-      <c r="G26" s="1">
-        <v>1</v>
-      </c>
-      <c r="H26" t="s">
-        <v>118</v>
-      </c>
-      <c r="I26" s="1">
+      <c r="H26" s="1">
+        <v>3</v>
+      </c>
+      <c r="I26" t="s">
+        <v>116</v>
+      </c>
+      <c r="J26" s="1">
         <v>25</v>
       </c>
-      <c r="J26" t="s">
-        <v>85</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0.28999999165534973</v>
-      </c>
-      <c r="L26" t="s">
-        <v>105</v>
+      <c r="K26" t="s">
+        <v>85</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0.38499999046325684</v>
       </c>
       <c r="M26" t="s">
         <v>105</v>
       </c>
       <c r="N26" t="s">
+        <v>105</v>
+      </c>
+      <c r="O26" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
-        <v>1</v>
+      <c r="A27" s="1">
+        <v>5317</v>
       </c>
       <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
         <v>99</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>16</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>105</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>108</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>41</v>
       </c>
-      <c r="G27" s="1">
-        <v>1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="H27" s="1">
+        <v>3</v>
+      </c>
+      <c r="I27" t="s">
+        <v>117</v>
+      </c>
+      <c r="J27" s="1">
         <v>25</v>
       </c>
-      <c r="J27" t="s">
-        <v>85</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0.27500000596046448</v>
-      </c>
-      <c r="L27" t="s">
-        <v>105</v>
+      <c r="K27" t="s">
+        <v>85</v>
+      </c>
+      <c r="L27" s="1">
+        <v>300</v>
       </c>
       <c r="M27" t="s">
         <v>105</v>
       </c>
       <c r="N27" t="s">
+        <v>105</v>
+      </c>
+      <c r="O27" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="s">
-        <v>1</v>
+      <c r="A28" s="1">
+        <v>5318</v>
       </c>
       <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
         <v>99</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>16</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>105</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>108</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>41</v>
       </c>
-      <c r="G28" s="1">
-        <v>1</v>
-      </c>
-      <c r="H28" t="s">
-        <v>120</v>
-      </c>
-      <c r="I28" s="1">
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>118</v>
+      </c>
+      <c r="J28" s="1">
         <v>25</v>
       </c>
-      <c r="J28" t="s">
-        <v>85</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0.28499999642372131</v>
-      </c>
-      <c r="L28" t="s">
-        <v>105</v>
+      <c r="K28" t="s">
+        <v>85</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0.28999999165534973</v>
       </c>
       <c r="M28" t="s">
         <v>105</v>
       </c>
       <c r="N28" t="s">
+        <v>105</v>
+      </c>
+      <c r="O28" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
+      <c r="A29" s="1">
+        <v>310</v>
+      </c>
+      <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>9</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>19</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>28</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>38</v>
       </c>
-      <c r="F29" t="s">
-        <v>40</v>
-      </c>
-      <c r="G29" s="1">
+      <c r="G29" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="1">
+        <v>3</v>
+      </c>
+      <c r="I29" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" t="s">
+        <v>85</v>
+      </c>
+      <c r="L29" s="1">
+        <v>500</v>
+      </c>
+      <c r="M29" t="s">
+        <v>28</v>
+      </c>
+      <c r="N29" t="s">
+        <v>91</v>
+      </c>
+      <c r="O29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1">
+        <v>309</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="1">
+        <v>3</v>
+      </c>
+      <c r="I30" t="s">
+        <v>58</v>
+      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" t="s">
+        <v>85</v>
+      </c>
+      <c r="L30" s="1">
+        <v>500</v>
+      </c>
+      <c r="M30" t="s">
+        <v>28</v>
+      </c>
+      <c r="N30" t="s">
+        <v>91</v>
+      </c>
+      <c r="O30" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1">
+        <v>307</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3</v>
+      </c>
+      <c r="I31" t="s">
+        <v>57</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" t="s">
+        <v>85</v>
+      </c>
+      <c r="L31" s="1">
+        <v>500</v>
+      </c>
+      <c r="M31" t="s">
+        <v>28</v>
+      </c>
+      <c r="N31" t="s">
+        <v>91</v>
+      </c>
+      <c r="O31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1">
+        <v>308</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" t="s">
+        <v>38</v>
+      </c>
+      <c r="G32" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="1">
         <v>2</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I32" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="1"/>
-      <c r="J29" t="s">
-        <v>85</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="J32" s="1"/>
+      <c r="K32" t="s">
+        <v>85</v>
+      </c>
+      <c r="L32" s="1">
         <v>500</v>
       </c>
-      <c r="L29" t="s">
+      <c r="M32" t="s">
         <v>28</v>
       </c>
-      <c r="M29" t="s">
+      <c r="N32" t="s">
         <v>91</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O32" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D30" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" t="s">
+    <row r="33">
+      <c r="A33" s="1">
+        <v>3879</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" t="s">
         <v>38</v>
       </c>
-      <c r="F30" t="s">
-        <v>40</v>
-      </c>
-      <c r="G30" s="1">
-        <v>3</v>
-      </c>
-      <c r="H30" t="s">
-        <v>57</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" t="s">
-        <v>85</v>
-      </c>
-      <c r="K30" s="1">
-        <v>500</v>
-      </c>
-      <c r="L30" t="s">
-        <v>28</v>
-      </c>
-      <c r="M30" t="s">
-        <v>91</v>
-      </c>
-      <c r="N30" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" t="s">
-        <v>38</v>
-      </c>
-      <c r="F31" t="s">
-        <v>40</v>
-      </c>
-      <c r="G31" s="1">
-        <v>3</v>
-      </c>
-      <c r="H31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31" s="1"/>
-      <c r="J31" t="s">
-        <v>85</v>
-      </c>
-      <c r="K31" s="1">
-        <v>500</v>
-      </c>
-      <c r="L31" t="s">
-        <v>28</v>
-      </c>
-      <c r="M31" t="s">
-        <v>91</v>
-      </c>
-      <c r="N31" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" t="s">
-        <v>28</v>
-      </c>
-      <c r="E32" t="s">
-        <v>38</v>
-      </c>
-      <c r="F32" t="s">
-        <v>40</v>
-      </c>
-      <c r="G32" s="1">
-        <v>3</v>
-      </c>
-      <c r="H32" t="s">
-        <v>58</v>
-      </c>
-      <c r="I32" s="1"/>
-      <c r="J32" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32" s="1">
-        <v>500</v>
-      </c>
-      <c r="L32" t="s">
-        <v>28</v>
-      </c>
-      <c r="M32" t="s">
-        <v>91</v>
-      </c>
-      <c r="N32" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" t="s">
-        <v>38</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
-        <v>61</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>62</v>
+      </c>
+      <c r="J33" s="1">
         <v>28.571428298950195</v>
       </c>
-      <c r="J33" t="s">
-        <v>85</v>
-      </c>
-      <c r="K33" s="1">
-        <v>190</v>
-      </c>
-      <c r="L33" t="s">
-        <v>29</v>
+      <c r="K33" t="s">
+        <v>85</v>
+      </c>
+      <c r="L33" s="1">
+        <v>175</v>
       </c>
       <c r="M33" t="s">
         <v>29</v>
       </c>
       <c r="N33" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
+      <c r="A34" s="1">
+        <v>3876</v>
+      </c>
+      <c r="B34" t="s">
         <v>2</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>10</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>29</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>38</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>41</v>
       </c>
-      <c r="G34" s="1">
-        <v>3</v>
-      </c>
-      <c r="H34" t="s">
-        <v>63</v>
-      </c>
-      <c r="I34" s="1">
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>61</v>
+      </c>
+      <c r="J34" s="1">
         <v>28.571428298950195</v>
       </c>
-      <c r="J34" t="s">
-        <v>85</v>
-      </c>
-      <c r="K34" s="1">
-        <v>250</v>
-      </c>
-      <c r="L34" t="s">
-        <v>29</v>
+      <c r="K34" t="s">
+        <v>85</v>
+      </c>
+      <c r="L34" s="1">
+        <v>190</v>
       </c>
       <c r="M34" t="s">
         <v>29</v>
       </c>
       <c r="N34" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
+      <c r="A35" s="1">
+        <v>3877</v>
+      </c>
+      <c r="B35" t="s">
         <v>2</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>10</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>20</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>29</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>38</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>41</v>
       </c>
-      <c r="G35" s="1">
-        <v>1</v>
-      </c>
-      <c r="H35" t="s">
-        <v>62</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="H35" s="1">
+        <v>3</v>
+      </c>
+      <c r="I35" t="s">
+        <v>63</v>
+      </c>
+      <c r="J35" s="1">
         <v>28.571428298950195</v>
       </c>
-      <c r="J35" t="s">
-        <v>85</v>
-      </c>
-      <c r="K35" s="1">
-        <v>175</v>
-      </c>
-      <c r="L35" t="s">
-        <v>29</v>
+      <c r="K35" t="s">
+        <v>85</v>
+      </c>
+      <c r="L35" s="1">
+        <v>250</v>
       </c>
       <c r="M35" t="s">
         <v>29</v>
       </c>
       <c r="N35" t="s">
+        <v>29</v>
+      </c>
+      <c r="O35" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s">
+      <c r="A36" s="1">
+        <v>3878</v>
+      </c>
+      <c r="B36" t="s">
         <v>2</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>10</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>20</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>29</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>38</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>41</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>2</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>60</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36" s="1">
         <v>28.571428298950195</v>
       </c>
-      <c r="J36" t="s">
-        <v>85</v>
-      </c>
-      <c r="K36" s="1">
+      <c r="K36" t="s">
+        <v>85</v>
+      </c>
+      <c r="L36" s="1">
         <v>190</v>
-      </c>
-      <c r="L36" t="s">
-        <v>29</v>
       </c>
       <c r="M36" t="s">
         <v>29</v>
       </c>
       <c r="N36" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="s">
+      <c r="A37" s="1">
+        <v>2673</v>
+      </c>
+      <c r="B37" t="s">
         <v>3</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>11</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>21</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>30</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>38</v>
       </c>
-      <c r="F37" t="s">
-        <v>40</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
-      <c r="H37" t="s">
+      <c r="G37" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
         <v>64</v>
       </c>
-      <c r="I37" s="1"/>
-      <c r="J37" t="s">
+      <c r="J37" s="1"/>
+      <c r="K37" t="s">
         <v>87</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <v>1.5</v>
-      </c>
-      <c r="L37" t="s">
-        <v>30</v>
       </c>
       <c r="M37" t="s">
         <v>30</v>
       </c>
       <c r="N37" t="s">
+        <v>30</v>
+      </c>
+      <c r="O37" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
-        <v>1</v>
+      <c r="A38" s="1">
+        <v>9372</v>
       </c>
       <c r="B38" t="s">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
         <v>100</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>102</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>106</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>38</v>
       </c>
-      <c r="F38" t="s">
-        <v>40</v>
-      </c>
-      <c r="G38" s="1">
-        <v>1</v>
-      </c>
-      <c r="H38" t="s">
+      <c r="G38" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
         <v>121</v>
       </c>
-      <c r="I38" s="1"/>
-      <c r="J38" t="s">
+      <c r="J38" s="1"/>
+      <c r="K38" t="s">
         <v>86</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>0.0013000000035390258</v>
-      </c>
-      <c r="L38" t="s">
-        <v>125</v>
       </c>
       <c r="M38" t="s">
         <v>125</v>
       </c>
       <c r="N38" t="s">
+        <v>125</v>
+      </c>
+      <c r="O38" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="s">
+      <c r="A39" s="1">
+        <v>4952</v>
+      </c>
+      <c r="B39" t="s">
         <v>2</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>12</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
         <v>22</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>31</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>38</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>41</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>3</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>65</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <v>125</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>86</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>500</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" t="s">
         <v>28</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" t="s">
         <v>91</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
-        <v>1</v>
+      <c r="A40" s="1">
+        <v>5463</v>
       </c>
       <c r="B40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
         <v>101</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>22</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>107</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>38</v>
       </c>
-      <c r="F40" t="s">
-        <v>40</v>
-      </c>
-      <c r="G40" s="1">
-        <v>1</v>
-      </c>
-      <c r="H40" t="s">
-        <v>122</v>
-      </c>
-      <c r="I40" s="1"/>
-      <c r="J40" t="s">
-        <v>85</v>
-      </c>
-      <c r="K40" s="1">
-        <v>500</v>
-      </c>
-      <c r="L40" t="s">
-        <v>107</v>
+      <c r="G40" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="1">
+        <v>3</v>
+      </c>
+      <c r="I40" t="s">
+        <v>124</v>
+      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" t="s">
+        <v>85</v>
+      </c>
+      <c r="L40" s="1">
+        <v>330</v>
       </c>
       <c r="M40" t="s">
         <v>107</v>
       </c>
       <c r="N40" t="s">
-        <v>94</v>
+        <v>107</v>
+      </c>
+      <c r="O40" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
-        <v>1</v>
+      <c r="A41" s="1">
+        <v>5464</v>
       </c>
       <c r="B41" t="s">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
         <v>101</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>22</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>107</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>38</v>
       </c>
-      <c r="F41" t="s">
-        <v>40</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1</v>
-      </c>
-      <c r="H41" t="s">
-        <v>123</v>
-      </c>
-      <c r="I41" s="1"/>
-      <c r="J41" t="s">
-        <v>85</v>
-      </c>
-      <c r="K41" s="1">
-        <v>330</v>
-      </c>
-      <c r="L41" t="s">
-        <v>107</v>
+      <c r="G41" t="s">
+        <v>40</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>122</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" t="s">
+        <v>85</v>
+      </c>
+      <c r="L41" s="1">
+        <v>500</v>
       </c>
       <c r="M41" t="s">
         <v>107</v>
       </c>
       <c r="N41" t="s">
-        <v>93</v>
+        <v>107</v>
+      </c>
+      <c r="O41" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s">
-        <v>1</v>
+      <c r="A42" s="1">
+        <v>5462</v>
       </c>
       <c r="B42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
         <v>101</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>22</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>107</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>38</v>
       </c>
-      <c r="F42" t="s">
-        <v>40</v>
-      </c>
-      <c r="G42" s="1">
-        <v>3</v>
-      </c>
-      <c r="H42" t="s">
-        <v>124</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" t="s">
-        <v>85</v>
-      </c>
-      <c r="K42" s="1">
+      <c r="G42" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>123</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" t="s">
+        <v>85</v>
+      </c>
+      <c r="L42" s="1">
         <v>330</v>
-      </c>
-      <c r="L42" t="s">
-        <v>107</v>
       </c>
       <c r="M42" t="s">
         <v>107</v>
       </c>
       <c r="N42" t="s">
+        <v>107</v>
+      </c>
+      <c r="O42" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
+      <c r="A43" s="1">
+        <v>2704</v>
+      </c>
+      <c r="B43" t="s">
         <v>3</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>11</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>22</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>32</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>38</v>
       </c>
-      <c r="F43" t="s">
-        <v>40</v>
-      </c>
-      <c r="G43" s="1">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>68</v>
-      </c>
-      <c r="I43" s="1"/>
-      <c r="J43" t="s">
-        <v>85</v>
-      </c>
-      <c r="K43" s="1">
+      <c r="G43" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>67</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" t="s">
+        <v>85</v>
+      </c>
+      <c r="L43" s="1">
         <v>350</v>
-      </c>
-      <c r="L43" t="s">
-        <v>32</v>
       </c>
       <c r="M43" t="s">
         <v>32</v>
       </c>
       <c r="N43" t="s">
+        <v>32</v>
+      </c>
+      <c r="O43" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" s="1">
+        <v>2703</v>
+      </c>
+      <c r="B44" t="s">
         <v>3</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>11</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>22</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>32</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>38</v>
       </c>
-      <c r="F44" t="s">
-        <v>40</v>
-      </c>
-      <c r="G44" s="1">
-        <v>1</v>
-      </c>
-      <c r="H44" t="s">
-        <v>67</v>
-      </c>
-      <c r="I44" s="1"/>
-      <c r="J44" t="s">
-        <v>85</v>
-      </c>
-      <c r="K44" s="1">
+      <c r="G44" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>66</v>
+      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" t="s">
+        <v>85</v>
+      </c>
+      <c r="L44" s="1">
         <v>350</v>
-      </c>
-      <c r="L44" t="s">
-        <v>32</v>
       </c>
       <c r="M44" t="s">
         <v>32</v>
       </c>
       <c r="N44" t="s">
+        <v>32</v>
+      </c>
+      <c r="O44" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s">
+      <c r="A45" s="1">
+        <v>2705</v>
+      </c>
+      <c r="B45" t="s">
         <v>3</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>11</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>22</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>32</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>38</v>
       </c>
-      <c r="F45" t="s">
-        <v>40</v>
-      </c>
-      <c r="G45" s="1">
-        <v>1</v>
-      </c>
-      <c r="H45" t="s">
-        <v>66</v>
-      </c>
-      <c r="I45" s="1"/>
-      <c r="J45" t="s">
-        <v>85</v>
-      </c>
-      <c r="K45" s="1">
+      <c r="G45" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>68</v>
+      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" t="s">
+        <v>85</v>
+      </c>
+      <c r="L45" s="1">
         <v>350</v>
-      </c>
-      <c r="L45" t="s">
-        <v>32</v>
       </c>
       <c r="M45" t="s">
         <v>32</v>
       </c>
       <c r="N45" t="s">
+        <v>32</v>
+      </c>
+      <c r="O45" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="s">
-        <v>1</v>
+      <c r="A46" s="1">
+        <v>10204</v>
       </c>
       <c r="B46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
         <v>13</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>18</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>33</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>38</v>
       </c>
-      <c r="F46" t="s">
-        <v>40</v>
-      </c>
-      <c r="G46" s="1">
+      <c r="G46" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="1">
         <v>3</v>
       </c>
-      <c r="H46" t="s">
-        <v>70</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" t="s">
+      <c r="I46" t="s">
+        <v>74</v>
+      </c>
+      <c r="J46" s="1"/>
+      <c r="K46" t="s">
         <v>86</v>
       </c>
-      <c r="K46" s="1">
-        <v>0.0065999999642372131</v>
-      </c>
-      <c r="L46" t="s">
-        <v>33</v>
+      <c r="L46" s="1">
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M46" t="s">
         <v>33</v>
       </c>
       <c r="N46" t="s">
+        <v>33</v>
+      </c>
+      <c r="O46" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
-        <v>1</v>
+      <c r="A47" s="1">
+        <v>10207</v>
       </c>
       <c r="B47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>18</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>33</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>38</v>
       </c>
-      <c r="F47" t="s">
-        <v>40</v>
-      </c>
-      <c r="G47" s="1">
-        <v>1</v>
-      </c>
-      <c r="H47" t="s">
-        <v>71</v>
-      </c>
-      <c r="I47" s="1"/>
-      <c r="J47" t="s">
-        <v>86</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0.0060000000521540642</v>
-      </c>
-      <c r="L47" t="s">
-        <v>33</v>
+      <c r="G47" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="1">
+        <v>2</v>
+      </c>
+      <c r="I47" t="s">
+        <v>75</v>
+      </c>
+      <c r="J47" s="1"/>
+      <c r="K47" t="s">
+        <v>87</v>
+      </c>
+      <c r="L47" s="1">
+        <v>21.670000076293945</v>
       </c>
       <c r="M47" t="s">
         <v>33</v>
       </c>
       <c r="N47" t="s">
-        <v>93</v>
+        <v>33</v>
+      </c>
+      <c r="O47" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>1</v>
+      <c r="A48" s="1">
+        <v>10209</v>
       </c>
       <c r="B48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
         <v>13</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>18</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>33</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>38</v>
       </c>
-      <c r="F48" t="s">
-        <v>40</v>
-      </c>
-      <c r="G48" s="1">
-        <v>3</v>
-      </c>
-      <c r="H48" t="s">
-        <v>74</v>
-      </c>
-      <c r="I48" s="1"/>
-      <c r="J48" t="s">
+      <c r="G48" t="s">
+        <v>40</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>71</v>
+      </c>
+      <c r="J48" s="1"/>
+      <c r="K48" t="s">
         <v>86</v>
       </c>
-      <c r="K48" s="1">
+      <c r="L48" s="1">
         <v>0.0060000000521540642</v>
-      </c>
-      <c r="L48" t="s">
-        <v>33</v>
       </c>
       <c r="M48" t="s">
         <v>33</v>
       </c>
       <c r="N48" t="s">
-        <v>94</v>
+        <v>33</v>
+      </c>
+      <c r="O48" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>1</v>
+      <c r="A49" s="1">
+        <v>10210</v>
       </c>
       <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
         <v>13</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>18</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>33</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>38</v>
       </c>
-      <c r="F49" t="s">
-        <v>40</v>
-      </c>
-      <c r="G49" s="1">
-        <v>1</v>
-      </c>
-      <c r="H49" t="s">
-        <v>69</v>
-      </c>
-      <c r="I49" s="1"/>
-      <c r="J49" t="s">
+      <c r="G49" t="s">
+        <v>40</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>73</v>
+      </c>
+      <c r="J49" s="1"/>
+      <c r="K49" t="s">
         <v>86</v>
       </c>
-      <c r="K49" s="1">
-        <v>0.0060000000521540642</v>
-      </c>
-      <c r="L49" t="s">
-        <v>33</v>
+      <c r="L49" s="1">
+        <v>6</v>
       </c>
       <c r="M49" t="s">
         <v>33</v>
       </c>
       <c r="N49" t="s">
-        <v>93</v>
+        <v>33</v>
+      </c>
+      <c r="O49" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="s">
-        <v>1</v>
+      <c r="A50" s="1">
+        <v>10208</v>
       </c>
       <c r="B50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
         <v>13</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>18</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>33</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>38</v>
       </c>
-      <c r="F50" t="s">
-        <v>40</v>
-      </c>
-      <c r="G50" s="1">
-        <v>2</v>
-      </c>
-      <c r="H50" t="s">
-        <v>76</v>
-      </c>
-      <c r="I50" s="1"/>
-      <c r="J50" t="s">
-        <v>87</v>
-      </c>
-      <c r="K50" s="1">
-        <v>21.479999542236328</v>
-      </c>
-      <c r="L50" t="s">
-        <v>33</v>
+      <c r="G50" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50" s="1">
+        <v>3</v>
+      </c>
+      <c r="I50" t="s">
+        <v>70</v>
+      </c>
+      <c r="J50" s="1"/>
+      <c r="K50" t="s">
+        <v>86</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0.0065999999642372131</v>
       </c>
       <c r="M50" t="s">
         <v>33</v>
       </c>
       <c r="N50" t="s">
+        <v>33</v>
+      </c>
+      <c r="O50" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s">
-        <v>1</v>
+      <c r="A51" s="1">
+        <v>10211</v>
       </c>
       <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
         <v>13</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>18</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>33</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>38</v>
       </c>
-      <c r="F51" t="s">
-        <v>40</v>
-      </c>
-      <c r="G51" s="1">
+      <c r="G51" t="s">
+        <v>40</v>
+      </c>
+      <c r="H51" s="1">
         <v>2</v>
       </c>
-      <c r="H51" t="s">
-        <v>75</v>
-      </c>
-      <c r="I51" s="1"/>
-      <c r="J51" t="s">
+      <c r="I51" t="s">
+        <v>76</v>
+      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" t="s">
         <v>87</v>
       </c>
-      <c r="K51" s="1">
-        <v>21.670000076293945</v>
-      </c>
-      <c r="L51" t="s">
-        <v>33</v>
+      <c r="L51" s="1">
+        <v>21.479999542236328</v>
       </c>
       <c r="M51" t="s">
         <v>33</v>
       </c>
       <c r="N51" t="s">
+        <v>33</v>
+      </c>
+      <c r="O51" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
-        <v>1</v>
+      <c r="A52" s="1">
+        <v>10205</v>
       </c>
       <c r="B52" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
         <v>13</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>18</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>33</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>38</v>
       </c>
-      <c r="F52" t="s">
-        <v>40</v>
-      </c>
-      <c r="G52" s="1">
-        <v>3</v>
-      </c>
-      <c r="H52" t="s">
-        <v>72</v>
-      </c>
-      <c r="I52" s="1"/>
-      <c r="J52" t="s">
-        <v>87</v>
-      </c>
-      <c r="K52" s="1">
-        <v>21.004999160766602</v>
-      </c>
-      <c r="L52" t="s">
-        <v>33</v>
+      <c r="G52" t="s">
+        <v>40</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" t="s">
+        <v>69</v>
+      </c>
+      <c r="J52" s="1"/>
+      <c r="K52" t="s">
+        <v>86</v>
+      </c>
+      <c r="L52" s="1">
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M52" t="s">
         <v>33</v>
       </c>
       <c r="N52" t="s">
-        <v>94</v>
+        <v>33</v>
+      </c>
+      <c r="O52" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="s">
-        <v>1</v>
+      <c r="A53" s="1">
+        <v>10206</v>
       </c>
       <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
         <v>13</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>18</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>33</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>38</v>
       </c>
-      <c r="F53" t="s">
-        <v>40</v>
-      </c>
-      <c r="G53" s="1">
-        <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>73</v>
-      </c>
-      <c r="I53" s="1"/>
-      <c r="J53" t="s">
-        <v>86</v>
-      </c>
-      <c r="K53" s="1">
-        <v>6</v>
-      </c>
-      <c r="L53" t="s">
-        <v>33</v>
+      <c r="G53" t="s">
+        <v>40</v>
+      </c>
+      <c r="H53" s="1">
+        <v>3</v>
+      </c>
+      <c r="I53" t="s">
+        <v>72</v>
+      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" t="s">
+        <v>87</v>
+      </c>
+      <c r="L53" s="1">
+        <v>21.004999160766602</v>
       </c>
       <c r="M53" t="s">
         <v>33</v>
       </c>
       <c r="N53" t="s">
+        <v>33</v>
+      </c>
+      <c r="O53" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="s">
-        <v>1</v>
+      <c r="A54" s="1">
+        <v>10214</v>
       </c>
       <c r="B54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
         <v>13</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>18</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>34</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>38</v>
       </c>
-      <c r="F54" t="s">
-        <v>40</v>
-      </c>
-      <c r="G54" s="1">
-        <v>1</v>
-      </c>
-      <c r="H54" t="s">
-        <v>78</v>
-      </c>
-      <c r="I54" s="1"/>
-      <c r="J54" t="s">
+      <c r="G54" t="s">
+        <v>40</v>
+      </c>
+      <c r="H54" s="1">
+        <v>1</v>
+      </c>
+      <c r="I54" t="s">
+        <v>80</v>
+      </c>
+      <c r="J54" s="1"/>
+      <c r="K54" t="s">
         <v>86</v>
       </c>
-      <c r="K54" s="1">
+      <c r="L54" s="1">
         <v>0.0099999997764825821</v>
-      </c>
-      <c r="L54" t="s">
-        <v>34</v>
       </c>
       <c r="M54" t="s">
         <v>34</v>
       </c>
       <c r="N54" t="s">
+        <v>34</v>
+      </c>
+      <c r="O54" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
-        <v>1</v>
+      <c r="A55" s="1">
+        <v>10215</v>
       </c>
       <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
         <v>13</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>18</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>34</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>38</v>
       </c>
-      <c r="F55" t="s">
-        <v>40</v>
-      </c>
-      <c r="G55" s="1">
+      <c r="G55" t="s">
+        <v>40</v>
+      </c>
+      <c r="H55" s="1">
         <v>3</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>79</v>
       </c>
-      <c r="I55" s="1"/>
-      <c r="J55" t="s">
+      <c r="J55" s="1"/>
+      <c r="K55" t="s">
         <v>86</v>
       </c>
-      <c r="K55" s="1">
+      <c r="L55" s="1">
         <v>0.0099999997764825821</v>
-      </c>
-      <c r="L55" t="s">
-        <v>34</v>
       </c>
       <c r="M55" t="s">
         <v>34</v>
       </c>
       <c r="N55" t="s">
+        <v>34</v>
+      </c>
+      <c r="O55" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
-        <v>1</v>
+      <c r="A56" s="1">
+        <v>10212</v>
       </c>
       <c r="B56" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
         <v>13</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>18</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>34</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>38</v>
       </c>
-      <c r="F56" t="s">
-        <v>40</v>
-      </c>
-      <c r="G56" s="1">
-        <v>1</v>
-      </c>
-      <c r="H56" t="s">
-        <v>80</v>
-      </c>
-      <c r="I56" s="1"/>
-      <c r="J56" t="s">
+      <c r="G56" t="s">
+        <v>40</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+      <c r="I56" t="s">
+        <v>78</v>
+      </c>
+      <c r="J56" s="1"/>
+      <c r="K56" t="s">
         <v>86</v>
       </c>
-      <c r="K56" s="1">
+      <c r="L56" s="1">
         <v>0.0099999997764825821</v>
-      </c>
-      <c r="L56" t="s">
-        <v>34</v>
       </c>
       <c r="M56" t="s">
         <v>34</v>
       </c>
       <c r="N56" t="s">
+        <v>34</v>
+      </c>
+      <c r="O56" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
-        <v>1</v>
+      <c r="A57" s="1">
+        <v>10213</v>
       </c>
       <c r="B57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
         <v>13</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>18</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>34</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>38</v>
       </c>
-      <c r="F57" t="s">
-        <v>40</v>
-      </c>
-      <c r="G57" s="1">
-        <v>1</v>
-      </c>
-      <c r="H57" t="s">
+      <c r="G57" t="s">
+        <v>40</v>
+      </c>
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+      <c r="I57" t="s">
         <v>77</v>
       </c>
-      <c r="I57" s="1"/>
-      <c r="J57" t="s">
+      <c r="J57" s="1"/>
+      <c r="K57" t="s">
         <v>86</v>
       </c>
-      <c r="K57" s="1">
+      <c r="L57" s="1">
         <v>0.0099999997764825821</v>
-      </c>
-      <c r="L57" t="s">
-        <v>34</v>
       </c>
       <c r="M57" t="s">
         <v>34</v>
       </c>
       <c r="N57" t="s">
+        <v>34</v>
+      </c>
+      <c r="O57" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="s">
-        <v>1</v>
+      <c r="A58" s="1">
+        <v>8411</v>
       </c>
       <c r="B58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
         <v>14</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>23</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>35</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>38</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>42</v>
       </c>
-      <c r="G58" s="1">
-        <v>1</v>
-      </c>
-      <c r="H58" t="s">
+      <c r="H58" s="1">
+        <v>1</v>
+      </c>
+      <c r="I58" t="s">
         <v>81</v>
       </c>
-      <c r="I58" s="1"/>
-      <c r="J58" t="s">
+      <c r="J58" s="1"/>
+      <c r="K58" t="s">
         <v>87</v>
       </c>
-      <c r="K58" s="1">
+      <c r="L58" s="1">
         <v>25</v>
-      </c>
-      <c r="L58" t="s">
-        <v>35</v>
       </c>
       <c r="M58" t="s">
         <v>35</v>
       </c>
       <c r="N58" t="s">
+        <v>35</v>
+      </c>
+      <c r="O58" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="s">
-        <v>1</v>
+      <c r="A59" s="1">
+        <v>8412</v>
       </c>
       <c r="B59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
         <v>14</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>23</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>35</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>38</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>42</v>
       </c>
-      <c r="G59" s="1">
-        <v>1</v>
-      </c>
-      <c r="H59" t="s">
+      <c r="H59" s="1">
+        <v>1</v>
+      </c>
+      <c r="I59" t="s">
         <v>82</v>
       </c>
-      <c r="I59" s="1"/>
-      <c r="J59" t="s">
+      <c r="J59" s="1"/>
+      <c r="K59" t="s">
         <v>87</v>
       </c>
-      <c r="K59" s="1">
+      <c r="L59" s="1">
         <v>25</v>
-      </c>
-      <c r="L59" t="s">
-        <v>35</v>
       </c>
       <c r="M59" t="s">
         <v>35</v>
       </c>
       <c r="N59" t="s">
+        <v>35</v>
+      </c>
+      <c r="O59" t="s">
         <v>97</v>
       </c>
     </row>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="14965" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15618" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>
@@ -671,7 +671,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>6761</v>
+        <v>6762</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -692,17 +692,17 @@
         <v>40</v>
       </c>
       <c r="H6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" t="s">
         <v>85</v>
       </c>
       <c r="L6" s="1">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="M6" t="s">
         <v>103</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>6759</v>
+        <v>6760</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -740,14 +740,14 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" t="s">
         <v>85</v>
       </c>
       <c r="L7" s="1">
-        <v>395</v>
+        <v>495</v>
       </c>
       <c r="M7" t="s">
         <v>103</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>6760</v>
+        <v>6761</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -782,17 +782,17 @@
         <v>40</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" t="s">
         <v>85</v>
       </c>
       <c r="L8" s="1">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="M8" t="s">
         <v>103</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>6762</v>
+        <v>6759</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -830,14 +830,14 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" t="s">
         <v>85</v>
       </c>
       <c r="L9" s="1">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M9" t="s">
         <v>103</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>4043</v>
+        <v>4042</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J11" s="1">
         <v>20</v>
@@ -931,7 +931,7 @@
         <v>85</v>
       </c>
       <c r="L11" s="1">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s">
         <v>104</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J12" s="1">
         <v>20</v>
@@ -978,7 +978,7 @@
         <v>85</v>
       </c>
       <c r="L12" s="1">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="M12" t="s">
         <v>104</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>4634</v>
+        <v>4632</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -1023,7 +1023,7 @@
         <v>85</v>
       </c>
       <c r="L13" s="1">
-        <v>0.25999999046325684</v>
+        <v>0.20000000298023224</v>
       </c>
       <c r="M13" t="s">
         <v>26</v>
@@ -1032,7 +1032,7 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1172,7 +1172,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>4632</v>
+        <v>4637</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -1193,17 +1193,17 @@
         <v>40</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" t="s">
         <v>85</v>
       </c>
       <c r="L17" s="1">
-        <v>0.20000000298023224</v>
+        <v>245</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -1212,12 +1212,12 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>4637</v>
+        <v>4634</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1238,17 +1238,17 @@
         <v>40</v>
       </c>
       <c r="H18" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" t="s">
         <v>85</v>
       </c>
       <c r="L18" s="1">
-        <v>245</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -1283,10 +1283,10 @@
         <v>40</v>
       </c>
       <c r="H19" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" t="s">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -1328,10 +1328,10 @@
         <v>40</v>
       </c>
       <c r="H20" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" t="s">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -1373,10 +1373,10 @@
         <v>40</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" t="s">
@@ -1487,7 +1487,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1">
-        <v>5319</v>
+        <v>5320</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
@@ -1508,10 +1508,10 @@
         <v>41</v>
       </c>
       <c r="H24" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I24" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="J24" s="1">
         <v>25</v>
@@ -1520,7 +1520,7 @@
         <v>85</v>
       </c>
       <c r="L24" s="1">
-        <v>0.27500000596046448</v>
+        <v>0.38499999046325684</v>
       </c>
       <c r="M24" t="s">
         <v>105</v>
@@ -1534,7 +1534,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>5321</v>
+        <v>5318</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J25" s="1">
         <v>25</v>
@@ -1567,7 +1567,7 @@
         <v>85</v>
       </c>
       <c r="L25" s="1">
-        <v>0.28499999642372131</v>
+        <v>0.28999999165534973</v>
       </c>
       <c r="M25" t="s">
         <v>105</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>5320</v>
+        <v>5321</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
@@ -1602,10 +1602,10 @@
         <v>41</v>
       </c>
       <c r="H26" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="J26" s="1">
         <v>25</v>
@@ -1614,7 +1614,7 @@
         <v>85</v>
       </c>
       <c r="L26" s="1">
-        <v>0.38499999046325684</v>
+        <v>0.28499999642372131</v>
       </c>
       <c r="M26" t="s">
         <v>105</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <v>5317</v>
+        <v>5319</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
@@ -1649,10 +1649,10 @@
         <v>41</v>
       </c>
       <c r="H27" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J27" s="1">
         <v>25</v>
@@ -1661,7 +1661,7 @@
         <v>85</v>
       </c>
       <c r="L27" s="1">
-        <v>300</v>
+        <v>0.27500000596046448</v>
       </c>
       <c r="M27" t="s">
         <v>105</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>5318</v>
+        <v>5317</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
@@ -1696,10 +1696,10 @@
         <v>41</v>
       </c>
       <c r="H28" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J28" s="1">
         <v>25</v>
@@ -1708,7 +1708,7 @@
         <v>85</v>
       </c>
       <c r="L28" s="1">
-        <v>0.28999999165534973</v>
+        <v>300</v>
       </c>
       <c r="M28" t="s">
         <v>105</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
@@ -1833,10 +1833,10 @@
         <v>40</v>
       </c>
       <c r="H31" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" t="s">
@@ -1857,7 +1857,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
@@ -1878,10 +1878,10 @@
         <v>40</v>
       </c>
       <c r="H32" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" t="s">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <v>3879</v>
+        <v>3877</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -1923,10 +1923,10 @@
         <v>41</v>
       </c>
       <c r="H33" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J33" s="1">
         <v>28.571428298950195</v>
@@ -1935,7 +1935,7 @@
         <v>85</v>
       </c>
       <c r="L33" s="1">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="M33" t="s">
         <v>29</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>3877</v>
+        <v>3879</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -2017,10 +2017,10 @@
         <v>41</v>
       </c>
       <c r="H35" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J35" s="1">
         <v>28.571428298950195</v>
@@ -2029,7 +2029,7 @@
         <v>85</v>
       </c>
       <c r="L35" s="1">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="M35" t="s">
         <v>29</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <v>5463</v>
+        <v>5462</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
@@ -2248,10 +2248,10 @@
         <v>40</v>
       </c>
       <c r="H40" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" t="s">
@@ -2272,7 +2272,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
@@ -2293,17 +2293,17 @@
         <v>40</v>
       </c>
       <c r="H41" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" t="s">
         <v>85</v>
       </c>
       <c r="L41" s="1">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="M41" t="s">
         <v>107</v>
@@ -2312,12 +2312,12 @@
         <v>107</v>
       </c>
       <c r="O41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <v>5462</v>
+        <v>5464</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
@@ -2341,14 +2341,14 @@
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" t="s">
         <v>85</v>
       </c>
       <c r="L42" s="1">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="M42" t="s">
         <v>107</v>
@@ -2357,12 +2357,12 @@
         <v>107</v>
       </c>
       <c r="O42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" t="s">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -2431,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" t="s">
@@ -2452,7 +2452,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
@@ -2476,7 +2476,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" t="s">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>10204</v>
+        <v>10209</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
@@ -2518,10 +2518,10 @@
         <v>40</v>
       </c>
       <c r="H46" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" t="s">
@@ -2537,7 +2537,7 @@
         <v>33</v>
       </c>
       <c r="O46" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47">
@@ -2587,7 +2587,7 @@
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>10209</v>
+        <v>10206</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
@@ -2608,17 +2608,17 @@
         <v>40</v>
       </c>
       <c r="H48" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L48" s="1">
-        <v>0.0060000000521540642</v>
+        <v>21.004999160766602</v>
       </c>
       <c r="M48" t="s">
         <v>33</v>
@@ -2627,12 +2627,12 @@
         <v>33</v>
       </c>
       <c r="O48" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <v>10210</v>
+        <v>10204</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
@@ -2653,17 +2653,17 @@
         <v>40</v>
       </c>
       <c r="H49" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" t="s">
         <v>86</v>
       </c>
       <c r="L49" s="1">
-        <v>6</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M49" t="s">
         <v>33</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <v>10208</v>
+        <v>10210</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
@@ -2698,17 +2698,17 @@
         <v>40</v>
       </c>
       <c r="H50" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" t="s">
         <v>86</v>
       </c>
       <c r="L50" s="1">
-        <v>0.0065999999642372131</v>
+        <v>6</v>
       </c>
       <c r="M50" t="s">
         <v>33</v>
@@ -2722,7 +2722,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>10211</v>
+        <v>10208</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
@@ -2743,17 +2743,17 @@
         <v>40</v>
       </c>
       <c r="H51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L51" s="1">
-        <v>21.479999542236328</v>
+        <v>0.0065999999642372131</v>
       </c>
       <c r="M51" t="s">
         <v>33</v>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <v>10205</v>
+        <v>10211</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
@@ -2788,17 +2788,17 @@
         <v>40</v>
       </c>
       <c r="H52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L52" s="1">
-        <v>0.0060000000521540642</v>
+        <v>21.479999542236328</v>
       </c>
       <c r="M52" t="s">
         <v>33</v>
@@ -2807,12 +2807,12 @@
         <v>33</v>
       </c>
       <c r="O52" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <v>10206</v>
+        <v>10205</v>
       </c>
       <c r="B53" t="s">
         <v>1</v>
@@ -2833,17 +2833,17 @@
         <v>40</v>
       </c>
       <c r="H53" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I53" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L53" s="1">
-        <v>21.004999160766602</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M53" t="s">
         <v>33</v>
@@ -2852,12 +2852,12 @@
         <v>33</v>
       </c>
       <c r="O53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <v>10214</v>
+        <v>10215</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
@@ -2878,10 +2878,10 @@
         <v>40</v>
       </c>
       <c r="H54" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I54" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" t="s">
@@ -2902,7 +2902,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <v>10215</v>
+        <v>10213</v>
       </c>
       <c r="B55" t="s">
         <v>1</v>
@@ -2923,10 +2923,10 @@
         <v>40</v>
       </c>
       <c r="H55" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" t="s">
@@ -2947,7 +2947,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <v>10212</v>
+        <v>10214</v>
       </c>
       <c r="B56" t="s">
         <v>1</v>
@@ -2971,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" t="s">
@@ -2992,7 +2992,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <v>10213</v>
+        <v>10212</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
@@ -3016,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" t="s">

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15618" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16924" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16924" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="17577" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="17577" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18230" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>
@@ -491,7 +491,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>6756</v>
+        <v>6755</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -512,17 +512,17 @@
         <v>40</v>
       </c>
       <c r="H2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" t="s">
         <v>85</v>
       </c>
       <c r="L2" s="1">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="M2" t="s">
         <v>25</v>
@@ -536,7 +536,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>6755</v>
+        <v>6758</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -557,17 +557,17 @@
         <v>40</v>
       </c>
       <c r="H3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" t="s">
         <v>85</v>
       </c>
       <c r="L3" s="1">
-        <v>325</v>
+        <v>235</v>
       </c>
       <c r="M3" t="s">
         <v>25</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>6757</v>
+        <v>6756</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -605,14 +605,14 @@
         <v>1</v>
       </c>
       <c r="I4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" t="s">
         <v>85</v>
       </c>
       <c r="L4" s="1">
-        <v>330</v>
+        <v>285</v>
       </c>
       <c r="M4" t="s">
         <v>25</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1">
-        <v>6758</v>
+        <v>6757</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
@@ -650,14 +650,14 @@
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" t="s">
         <v>85</v>
       </c>
       <c r="L5" s="1">
-        <v>235</v>
+        <v>330</v>
       </c>
       <c r="M5" t="s">
         <v>25</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>6762</v>
+        <v>6759</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -695,14 +695,14 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" t="s">
         <v>85</v>
       </c>
       <c r="L6" s="1">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M6" t="s">
         <v>103</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>6759</v>
+        <v>6762</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -830,14 +830,14 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" t="s">
         <v>85</v>
       </c>
       <c r="L9" s="1">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M9" t="s">
         <v>103</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>4044</v>
+        <v>4043</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -875,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J10" s="1">
         <v>20</v>
@@ -884,7 +884,7 @@
         <v>85</v>
       </c>
       <c r="L10" s="1">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s">
         <v>104</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J12" s="1">
         <v>20</v>
@@ -978,7 +978,7 @@
         <v>85</v>
       </c>
       <c r="L12" s="1">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="M12" t="s">
         <v>104</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>4632</v>
+        <v>4633</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -1023,7 +1023,7 @@
         <v>85</v>
       </c>
       <c r="L13" s="1">
-        <v>0.20000000298023224</v>
+        <v>0.2199999988079071</v>
       </c>
       <c r="M13" t="s">
         <v>26</v>
@@ -1032,12 +1032,12 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1">
-        <v>4636</v>
+        <v>4635</v>
       </c>
       <c r="B14" t="s">
         <v>2</v>
@@ -1068,7 +1068,7 @@
         <v>85</v>
       </c>
       <c r="L14" s="1">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s">
         <v>26</v>
@@ -1077,12 +1077,12 @@
         <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>4635</v>
+        <v>4634</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -1103,17 +1103,17 @@
         <v>40</v>
       </c>
       <c r="H15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" t="s">
         <v>85</v>
       </c>
       <c r="L15" s="1">
-        <v>170</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="M15" t="s">
         <v>26</v>
@@ -1122,12 +1122,12 @@
         <v>26</v>
       </c>
       <c r="O15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>4633</v>
+        <v>4637</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -1148,17 +1148,17 @@
         <v>40</v>
       </c>
       <c r="H16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" t="s">
         <v>85</v>
       </c>
       <c r="L16" s="1">
-        <v>0.2199999988079071</v>
+        <v>245</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
@@ -1167,12 +1167,12 @@
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>4637</v>
+        <v>4636</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -1203,7 +1203,7 @@
         <v>85</v>
       </c>
       <c r="L17" s="1">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -1212,12 +1212,12 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>4634</v>
+        <v>4632</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1248,7 +1248,7 @@
         <v>85</v>
       </c>
       <c r="L18" s="1">
-        <v>0.25999999046325684</v>
+        <v>0.20000000298023224</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -1257,12 +1257,12 @@
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -1286,7 +1286,7 @@
         <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" t="s">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" t="s">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>5318</v>
+        <v>5321</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J25" s="1">
         <v>25</v>
@@ -1567,7 +1567,7 @@
         <v>85</v>
       </c>
       <c r="L25" s="1">
-        <v>0.28999999165534973</v>
+        <v>0.28499999642372131</v>
       </c>
       <c r="M25" t="s">
         <v>105</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>5321</v>
+        <v>5317</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
@@ -1602,10 +1602,10 @@
         <v>41</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I26" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J26" s="1">
         <v>25</v>
@@ -1614,7 +1614,7 @@
         <v>85</v>
       </c>
       <c r="L26" s="1">
-        <v>0.28499999642372131</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s">
         <v>105</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <v>5319</v>
+        <v>5318</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
@@ -1652,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J27" s="1">
         <v>25</v>
@@ -1661,7 +1661,7 @@
         <v>85</v>
       </c>
       <c r="L27" s="1">
-        <v>0.27500000596046448</v>
+        <v>0.28999999165534973</v>
       </c>
       <c r="M27" t="s">
         <v>105</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>5317</v>
+        <v>5319</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
@@ -1696,10 +1696,10 @@
         <v>41</v>
       </c>
       <c r="H28" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J28" s="1">
         <v>25</v>
@@ -1708,7 +1708,7 @@
         <v>85</v>
       </c>
       <c r="L28" s="1">
-        <v>300</v>
+        <v>0.27500000596046448</v>
       </c>
       <c r="M28" t="s">
         <v>105</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="29">
       <c r="A29" s="1">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
@@ -1746,7 +1746,7 @@
         <v>3</v>
       </c>
       <c r="I29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" t="s">
@@ -1767,7 +1767,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -1788,10 +1788,10 @@
         <v>40</v>
       </c>
       <c r="H30" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" t="s">
@@ -1812,7 +1812,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
@@ -1833,10 +1833,10 @@
         <v>40</v>
       </c>
       <c r="H31" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J31" s="1"/>
       <c r="K31" t="s">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <v>3876</v>
+        <v>3879</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -1973,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J34" s="1">
         <v>28.571428298950195</v>
@@ -1982,7 +1982,7 @@
         <v>85</v>
       </c>
       <c r="L34" s="1">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M34" t="s">
         <v>29</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>3879</v>
+        <v>3876</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -2020,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J35" s="1">
         <v>28.571428298950195</v>
@@ -2029,7 +2029,7 @@
         <v>85</v>
       </c>
       <c r="L35" s="1">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="M35" t="s">
         <v>29</v>
@@ -2272,7 +2272,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <v>5463</v>
+        <v>5464</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
@@ -2293,17 +2293,17 @@
         <v>40</v>
       </c>
       <c r="H41" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" t="s">
         <v>85</v>
       </c>
       <c r="L41" s="1">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="M41" t="s">
         <v>107</v>
@@ -2312,12 +2312,12 @@
         <v>107</v>
       </c>
       <c r="O41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1">
-        <v>5464</v>
+        <v>5463</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
@@ -2338,17 +2338,17 @@
         <v>40</v>
       </c>
       <c r="H42" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" t="s">
         <v>85</v>
       </c>
       <c r="L42" s="1">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="M42" t="s">
         <v>107</v>
@@ -2357,12 +2357,12 @@
         <v>107</v>
       </c>
       <c r="O42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" t="s">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -2431,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" t="s">
@@ -2452,7 +2452,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>2703</v>
+        <v>2705</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
@@ -2476,7 +2476,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" t="s">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>10209</v>
+        <v>10206</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
@@ -2518,17 +2518,17 @@
         <v>40</v>
       </c>
       <c r="H46" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L46" s="1">
-        <v>0.0060000000521540642</v>
+        <v>21.004999160766602</v>
       </c>
       <c r="M46" t="s">
         <v>33</v>
@@ -2537,12 +2537,12 @@
         <v>33</v>
       </c>
       <c r="O46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <v>10207</v>
+        <v>10209</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
@@ -2563,17 +2563,17 @@
         <v>40</v>
       </c>
       <c r="H47" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L47" s="1">
-        <v>21.670000076293945</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M47" t="s">
         <v>33</v>
@@ -2582,12 +2582,12 @@
         <v>33</v>
       </c>
       <c r="O47" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>10206</v>
+        <v>10208</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
@@ -2611,14 +2611,14 @@
         <v>3</v>
       </c>
       <c r="I48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L48" s="1">
-        <v>21.004999160766602</v>
+        <v>0.0065999999642372131</v>
       </c>
       <c r="M48" t="s">
         <v>33</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1">
-        <v>10204</v>
+        <v>10205</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
@@ -2653,10 +2653,10 @@
         <v>40</v>
       </c>
       <c r="H49" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" t="s">
@@ -2672,7 +2672,7 @@
         <v>33</v>
       </c>
       <c r="O49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50">
@@ -2722,7 +2722,7 @@
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>10208</v>
+        <v>10207</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
@@ -2743,17 +2743,17 @@
         <v>40</v>
       </c>
       <c r="H51" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I51" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L51" s="1">
-        <v>0.0065999999642372131</v>
+        <v>21.670000076293945</v>
       </c>
       <c r="M51" t="s">
         <v>33</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <v>10205</v>
+        <v>10204</v>
       </c>
       <c r="B53" t="s">
         <v>1</v>
@@ -2833,10 +2833,10 @@
         <v>40</v>
       </c>
       <c r="H53" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" t="s">
@@ -2852,7 +2852,7 @@
         <v>33</v>
       </c>
       <c r="O53" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54">
@@ -2947,7 +2947,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1">
-        <v>10214</v>
+        <v>10212</v>
       </c>
       <c r="B56" t="s">
         <v>1</v>
@@ -2971,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="I56" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" t="s">
@@ -2992,7 +2992,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1">
-        <v>10212</v>
+        <v>10214</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
@@ -3016,7 +3016,7 @@
         <v>1</v>
       </c>
       <c r="I57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" t="s">

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="18230" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19536" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19536" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20189" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20189" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22148" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="22148" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24107" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24107" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24760" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24760" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26719" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>
@@ -491,7 +491,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1">
-        <v>6755</v>
+        <v>6758</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -512,17 +512,17 @@
         <v>40</v>
       </c>
       <c r="H2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" t="s">
         <v>85</v>
       </c>
       <c r="L2" s="1">
-        <v>325</v>
+        <v>235</v>
       </c>
       <c r="M2" t="s">
         <v>25</v>
@@ -536,7 +536,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1">
-        <v>6758</v>
+        <v>6756</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -560,14 +560,14 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" t="s">
         <v>85</v>
       </c>
       <c r="L3" s="1">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="M3" t="s">
         <v>25</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1">
-        <v>6756</v>
+        <v>6755</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -602,17 +602,17 @@
         <v>40</v>
       </c>
       <c r="H4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" t="s">
         <v>85</v>
       </c>
       <c r="L4" s="1">
-        <v>285</v>
+        <v>325</v>
       </c>
       <c r="M4" t="s">
         <v>25</v>
@@ -671,7 +671,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1">
-        <v>6759</v>
+        <v>6762</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -695,14 +695,14 @@
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" t="s">
         <v>85</v>
       </c>
       <c r="L6" s="1">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="M6" t="s">
         <v>103</v>
@@ -716,7 +716,7 @@
     </row>
     <row r="7">
       <c r="A7" s="1">
-        <v>6760</v>
+        <v>6761</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
@@ -737,17 +737,17 @@
         <v>40</v>
       </c>
       <c r="H7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" t="s">
         <v>85</v>
       </c>
       <c r="L7" s="1">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="M7" t="s">
         <v>103</v>
@@ -761,7 +761,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1">
-        <v>6761</v>
+        <v>6760</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
@@ -782,17 +782,17 @@
         <v>40</v>
       </c>
       <c r="H8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" t="s">
         <v>85</v>
       </c>
       <c r="L8" s="1">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M8" t="s">
         <v>103</v>
@@ -806,7 +806,7 @@
     </row>
     <row r="9">
       <c r="A9" s="1">
-        <v>6762</v>
+        <v>6759</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -830,14 +830,14 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" t="s">
         <v>85</v>
       </c>
       <c r="L9" s="1">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M9" t="s">
         <v>103</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="10">
       <c r="A10" s="1">
-        <v>4043</v>
+        <v>4044</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -875,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1">
         <v>20</v>
@@ -884,7 +884,7 @@
         <v>85</v>
       </c>
       <c r="L10" s="1">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s">
         <v>104</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J11" s="1">
         <v>20</v>
@@ -931,7 +931,7 @@
         <v>85</v>
       </c>
       <c r="L11" s="1">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="M11" t="s">
         <v>104</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1">
-        <v>4044</v>
+        <v>4042</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -969,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J12" s="1">
         <v>20</v>
@@ -978,7 +978,7 @@
         <v>85</v>
       </c>
       <c r="L12" s="1">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s">
         <v>104</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1">
-        <v>4633</v>
+        <v>4632</v>
       </c>
       <c r="B13" t="s">
         <v>2</v>
@@ -1023,7 +1023,7 @@
         <v>85</v>
       </c>
       <c r="L13" s="1">
-        <v>0.2199999988079071</v>
+        <v>0.20000000298023224</v>
       </c>
       <c r="M13" t="s">
         <v>26</v>
@@ -1032,7 +1032,7 @@
         <v>26</v>
       </c>
       <c r="O13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1082,7 +1082,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1">
-        <v>4634</v>
+        <v>4637</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -1103,17 +1103,17 @@
         <v>40</v>
       </c>
       <c r="H15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" t="s">
         <v>85</v>
       </c>
       <c r="L15" s="1">
-        <v>0.25999999046325684</v>
+        <v>245</v>
       </c>
       <c r="M15" t="s">
         <v>26</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1">
-        <v>4637</v>
+        <v>4633</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -1148,17 +1148,17 @@
         <v>40</v>
       </c>
       <c r="H16" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" t="s">
         <v>85</v>
       </c>
       <c r="L16" s="1">
-        <v>245</v>
+        <v>0.2199999988079071</v>
       </c>
       <c r="M16" t="s">
         <v>26</v>
@@ -1167,12 +1167,12 @@
         <v>26</v>
       </c>
       <c r="O16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1">
-        <v>4636</v>
+        <v>4634</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -1193,17 +1193,17 @@
         <v>40</v>
       </c>
       <c r="H17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" t="s">
         <v>85</v>
       </c>
       <c r="L17" s="1">
-        <v>220</v>
+        <v>0.25999999046325684</v>
       </c>
       <c r="M17" t="s">
         <v>26</v>
@@ -1212,12 +1212,12 @@
         <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1">
-        <v>4632</v>
+        <v>4636</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1238,17 +1238,17 @@
         <v>40</v>
       </c>
       <c r="H18" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" t="s">
         <v>85</v>
       </c>
       <c r="L18" s="1">
-        <v>0.20000000298023224</v>
+        <v>220</v>
       </c>
       <c r="M18" t="s">
         <v>26</v>
@@ -1257,12 +1257,12 @@
         <v>26</v>
       </c>
       <c r="O18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1">
-        <v>2332</v>
+        <v>2329</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -1286,7 +1286,7 @@
         <v>3</v>
       </c>
       <c r="I19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" t="s">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -1328,10 +1328,10 @@
         <v>40</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" t="s">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -1373,10 +1373,10 @@
         <v>40</v>
       </c>
       <c r="H21" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" t="s">
@@ -1397,7 +1397,7 @@
     </row>
     <row r="22">
       <c r="A22" s="1">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -1421,7 +1421,7 @@
         <v>3</v>
       </c>
       <c r="I22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" t="s">
@@ -1442,7 +1442,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -1463,10 +1463,10 @@
         <v>40</v>
       </c>
       <c r="H23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" t="s">
@@ -1534,7 +1534,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1">
-        <v>5321</v>
+        <v>5318</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J25" s="1">
         <v>25</v>
@@ -1567,7 +1567,7 @@
         <v>85</v>
       </c>
       <c r="L25" s="1">
-        <v>0.28499999642372131</v>
+        <v>0.28999999165534973</v>
       </c>
       <c r="M25" t="s">
         <v>105</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1">
-        <v>5317</v>
+        <v>5319</v>
       </c>
       <c r="B26" t="s">
         <v>1</v>
@@ -1602,10 +1602,10 @@
         <v>41</v>
       </c>
       <c r="H26" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J26" s="1">
         <v>25</v>
@@ -1614,7 +1614,7 @@
         <v>85</v>
       </c>
       <c r="L26" s="1">
-        <v>300</v>
+        <v>0.27500000596046448</v>
       </c>
       <c r="M26" t="s">
         <v>105</v>
@@ -1628,7 +1628,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1">
-        <v>5318</v>
+        <v>5317</v>
       </c>
       <c r="B27" t="s">
         <v>1</v>
@@ -1649,10 +1649,10 @@
         <v>41</v>
       </c>
       <c r="H27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J27" s="1">
         <v>25</v>
@@ -1661,7 +1661,7 @@
         <v>85</v>
       </c>
       <c r="L27" s="1">
-        <v>0.28999999165534973</v>
+        <v>300</v>
       </c>
       <c r="M27" t="s">
         <v>105</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="28">
       <c r="A28" s="1">
-        <v>5319</v>
+        <v>5321</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
@@ -1699,7 +1699,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J28" s="1">
         <v>25</v>
@@ -1708,7 +1708,7 @@
         <v>85</v>
       </c>
       <c r="L28" s="1">
-        <v>0.27500000596046448</v>
+        <v>0.28499999642372131</v>
       </c>
       <c r="M28" t="s">
         <v>105</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
@@ -1788,10 +1788,10 @@
         <v>40</v>
       </c>
       <c r="H30" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" t="s">
@@ -1857,7 +1857,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
@@ -1878,10 +1878,10 @@
         <v>40</v>
       </c>
       <c r="H32" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" t="s">
@@ -1902,7 +1902,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1">
-        <v>3877</v>
+        <v>3878</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -1923,10 +1923,10 @@
         <v>41</v>
       </c>
       <c r="H33" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I33" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J33" s="1">
         <v>28.571428298950195</v>
@@ -1935,7 +1935,7 @@
         <v>85</v>
       </c>
       <c r="L33" s="1">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="M33" t="s">
         <v>29</v>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="34">
       <c r="A34" s="1">
-        <v>3879</v>
+        <v>3876</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -1973,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J34" s="1">
         <v>28.571428298950195</v>
@@ -1982,7 +1982,7 @@
         <v>85</v>
       </c>
       <c r="L34" s="1">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="M34" t="s">
         <v>29</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="35">
       <c r="A35" s="1">
-        <v>3876</v>
+        <v>3879</v>
       </c>
       <c r="B35" t="s">
         <v>2</v>
@@ -2020,7 +2020,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J35" s="1">
         <v>28.571428298950195</v>
@@ -2029,7 +2029,7 @@
         <v>85</v>
       </c>
       <c r="L35" s="1">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="M35" t="s">
         <v>29</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="36">
       <c r="A36" s="1">
-        <v>3878</v>
+        <v>3877</v>
       </c>
       <c r="B36" t="s">
         <v>2</v>
@@ -2064,10 +2064,10 @@
         <v>41</v>
       </c>
       <c r="H36" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J36" s="1">
         <v>28.571428298950195</v>
@@ -2076,7 +2076,7 @@
         <v>85</v>
       </c>
       <c r="L36" s="1">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s">
         <v>29</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="40">
       <c r="A40" s="1">
-        <v>5462</v>
+        <v>5464</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
@@ -2251,14 +2251,14 @@
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" t="s">
         <v>85</v>
       </c>
       <c r="L40" s="1">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="M40" t="s">
         <v>107</v>
@@ -2267,12 +2267,12 @@
         <v>107</v>
       </c>
       <c r="O40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1">
-        <v>5464</v>
+        <v>5462</v>
       </c>
       <c r="B41" t="s">
         <v>1</v>
@@ -2296,14 +2296,14 @@
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" t="s">
         <v>85</v>
       </c>
       <c r="L41" s="1">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="M41" t="s">
         <v>107</v>
@@ -2312,7 +2312,7 @@
         <v>107</v>
       </c>
       <c r="O41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42">
@@ -2362,7 +2362,7 @@
     </row>
     <row r="43">
       <c r="A43" s="1">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" t="s">
@@ -2407,7 +2407,7 @@
     </row>
     <row r="44">
       <c r="A44" s="1">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -2431,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" t="s">
@@ -2452,7 +2452,7 @@
     </row>
     <row r="45">
       <c r="A45" s="1">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
@@ -2476,7 +2476,7 @@
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" t="s">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="46">
       <c r="A46" s="1">
-        <v>10206</v>
+        <v>10207</v>
       </c>
       <c r="B46" t="s">
         <v>1</v>
@@ -2518,17 +2518,17 @@
         <v>40</v>
       </c>
       <c r="H46" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" t="s">
         <v>87</v>
       </c>
       <c r="L46" s="1">
-        <v>21.004999160766602</v>
+        <v>21.670000076293945</v>
       </c>
       <c r="M46" t="s">
         <v>33</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="47">
       <c r="A47" s="1">
-        <v>10209</v>
+        <v>10210</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
@@ -2566,14 +2566,14 @@
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" t="s">
         <v>86</v>
       </c>
       <c r="L47" s="1">
-        <v>0.0060000000521540642</v>
+        <v>6</v>
       </c>
       <c r="M47" t="s">
         <v>33</v>
@@ -2582,12 +2582,12 @@
         <v>33</v>
       </c>
       <c r="O47" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1">
-        <v>10208</v>
+        <v>10204</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
@@ -2611,14 +2611,14 @@
         <v>3</v>
       </c>
       <c r="I48" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" t="s">
         <v>86</v>
       </c>
       <c r="L48" s="1">
-        <v>0.0065999999642372131</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M48" t="s">
         <v>33</v>
@@ -2677,7 +2677,7 @@
     </row>
     <row r="50">
       <c r="A50" s="1">
-        <v>10210</v>
+        <v>10209</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
@@ -2701,14 +2701,14 @@
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" t="s">
         <v>86</v>
       </c>
       <c r="L50" s="1">
-        <v>6</v>
+        <v>0.0060000000521540642</v>
       </c>
       <c r="M50" t="s">
         <v>33</v>
@@ -2717,12 +2717,12 @@
         <v>33</v>
       </c>
       <c r="O50" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1">
-        <v>10207</v>
+        <v>10208</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
@@ -2743,17 +2743,17 @@
         <v>40</v>
       </c>
       <c r="H51" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L51" s="1">
-        <v>21.670000076293945</v>
+        <v>0.0065999999642372131</v>
       </c>
       <c r="M51" t="s">
         <v>33</v>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="52">
       <c r="A52" s="1">
-        <v>10211</v>
+        <v>10206</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
@@ -2788,17 +2788,17 @@
         <v>40</v>
       </c>
       <c r="H52" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" t="s">
         <v>87</v>
       </c>
       <c r="L52" s="1">
-        <v>21.479999542236328</v>
+        <v>21.004999160766602</v>
       </c>
       <c r="M52" t="s">
         <v>33</v>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="53">
       <c r="A53" s="1">
-        <v>10204</v>
+        <v>10211</v>
       </c>
       <c r="B53" t="s">
         <v>1</v>
@@ -2833,17 +2833,17 @@
         <v>40</v>
       </c>
       <c r="H53" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L53" s="1">
-        <v>0.0060000000521540642</v>
+        <v>21.479999542236328</v>
       </c>
       <c r="M53" t="s">
         <v>33</v>
@@ -2857,7 +2857,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1">
-        <v>10215</v>
+        <v>10213</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
@@ -2878,10 +2878,10 @@
         <v>40</v>
       </c>
       <c r="H54" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" t="s">
@@ -2902,7 +2902,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1">
-        <v>10213</v>
+        <v>10215</v>
       </c>
       <c r="B55" t="s">
         <v>1</v>
@@ -2923,10 +2923,10 @@
         <v>40</v>
       </c>
       <c r="H55" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" t="s">
@@ -3037,7 +3037,7 @@
     </row>
     <row r="58">
       <c r="A58" s="1">
-        <v>8411</v>
+        <v>8412</v>
       </c>
       <c r="B58" t="s">
         <v>1</v>
@@ -3061,7 +3061,7 @@
         <v>1</v>
       </c>
       <c r="I58" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" t="s">
@@ -3082,7 +3082,7 @@
     </row>
     <row r="59">
       <c r="A59" s="1">
-        <v>8412</v>
+        <v>8411</v>
       </c>
       <c r="B59" t="s">
         <v>1</v>
@@ -3106,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" t="s">

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26719" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27372" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="27372" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="28025" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="28025" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29984" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29984" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30637" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30637" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="29984" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30637" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="32596" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="32596" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33249" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33249" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33902" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="33902" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35208" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="35208" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37167" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
+++ b/outputs/master_rename_build/tables/excluded_standard_unit_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="37167" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="38473" uniqueCount="127">
   <si>
     <t>pull_province</t>
   </si>
